--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -601,7 +601,7 @@
         <v>45954</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45110</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45419</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45586</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45376</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46164</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>46254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46253</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46267</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45952</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>44966</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>46164</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45425</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45751</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>46170</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45979</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45422</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44477</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>45889</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>45323</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>45939</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>45679</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44853</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>45519</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>46253</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>46240</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>45804</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         <v>45819</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45517</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>44953</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>45875</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>44966</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45813</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>45412</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>44966</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>46205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>45889</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45456</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45939</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>45875</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>45118</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45932</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>45897</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>46091</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45940</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>45783</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>45678</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>44776</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>45187</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>46164</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45776</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45412</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>45813</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45517</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>46195</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>44806</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>45945</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>46177</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45856</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44806</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>44602</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>45233</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>45385</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>46128</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>46253</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45813</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>46237</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>44474</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>44900</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>44806</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45936</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45450</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>45994</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>44928</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44712</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>44607</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45875</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44845</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>46045</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45545</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>46244</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>46029</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>44477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>46178</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>45772</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45771</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45834</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45834</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>44943</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44503</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>44529</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44572</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         <v>45769</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45944</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>45954</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45209</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>45985</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>46176</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>45880</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>46127</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45811</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45236</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>46262</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>46178</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>46237</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>46237</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45999</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44860</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>45015</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>44462</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44791</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45588</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45712</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45608</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45904</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>44978</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45931</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45931</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45932</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45736</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>46153</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>46150</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>45954</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>45960</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45475</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>44806</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45490</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45989</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44875</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>46049</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>46064</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>46069</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>46198</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45804</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>46199</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45933</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>46244</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>46204</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>46094</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>45555</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>45470</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44473</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>45237</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44986</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>46266</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45478</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18474,7 +18474,7 @@
         <v>46258</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45782</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45643</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>46233</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>45818</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45789</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>45782</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>46241</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45868</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45877</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>44860</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45016</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45118</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45016</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>45904</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>46049</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44826</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45595</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45200</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>45434</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45092</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45439</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45511</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45527</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>46139</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>46136</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>45533</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45196</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45936</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45943</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45555</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45594</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21971,7 +21971,7 @@
         <v>46153</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>46157</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45959</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>46006</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>46006</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>45960</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>46006</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>44529</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>46182</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45517</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>44606</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>45909</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>46188</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45384</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45200</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45888</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>46197</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>45236</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>46107</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>46112</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>46199</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>46244</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>46244</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>46204</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24607,7 +24607,7 @@
         <v>46134</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>46136</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45560</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>46253</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>44841</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45384</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>46029</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>44477</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>44473</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45511</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>45260</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45615</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45517</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>46282</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45840</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>45853</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>45856</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>45118</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>44546</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44586</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44575</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>44536</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>44579</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>44834</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>44587</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>44529</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44839</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44729</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>44872</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>44564</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44536</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>44487</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>44573</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>44587</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44810</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44698</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44530</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>44615</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44694</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>44575</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44714</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>44847</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44648</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>44839</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>44529</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>44599</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>44529</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>44810</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         <v>44594</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44594</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>44795</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45365</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45359</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>45533</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45534</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>44837</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>45625</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45063</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45532</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45267</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45670</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45191</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45231</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45183</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>45351</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>45419</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>45419</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>45583</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45743</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>45278</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>45280</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45426</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45484</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>45419</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>44951</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45638</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>44923</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45511</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45170</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44712</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44909</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>44909</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45203</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45258</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>44487</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>44740</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45268</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45387</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45426</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45611</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>45119</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45701</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>44459</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>45568</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>45343</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>45539</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45370</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>44715</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>45289</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>45279</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45356</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45131</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45009</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45306</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>45630</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>45082</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>45712</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45526</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>45154</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45548</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45708</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45749</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45476</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>46139</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>45586</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>46031</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>45595</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46136</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45670</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45525</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>46136</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45786</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45294</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>44853</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>44909</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>46136</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>46136</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>46139</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45201</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45390</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45042</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>46136</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35065,7 +35065,7 @@
         <v>45217</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>45888</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45294</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>46136</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45581</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45293</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>45890</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45890</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45815</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>46139</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45327</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>45895</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45895</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45895</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45455</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45455</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>46136</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45838</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45266</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45897</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>46136</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>46136</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>46136</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>45896</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>46136</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>46136</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>45897</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45897</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>45898</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45898</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46136</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>46139</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45693</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45483</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>44903</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45903</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45351</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45905</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>46136</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45905</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45805</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>45908</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>45264</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
         <v>45266</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>45266</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>44902</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45989</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45996</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>45911</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>45911</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>45911</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38903,7 +38903,7 @@
         <v>45812</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45915</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45730</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>46090</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>45915</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45215</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45915</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>44902</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39497,7 +39497,7 @@
         <v>44606</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>45917</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45919</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>45919</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         <v>45919</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39872,7 +39872,7 @@
         <v>44775</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>45407</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45923</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>45922</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45351</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45265</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>45553</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>45219</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46142</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>44685</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>46121</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>46142</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>46142</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45930</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45931</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45930</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45931</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>46146</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>46146</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>46146</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>45933</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>46147</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45208</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>45208</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45674</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>45595</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45524</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>45050</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>46146</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>45943</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>44979</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45943</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>46148</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>45944</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45944</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45911</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45945</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>45280</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
         <v>45280</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45636</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45947</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45945</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45947</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45947</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>46148</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>45947</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>45950</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>46153</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>46153</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>45950</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43597,7 +43597,7 @@
         <v>46153</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>45330</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45953</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>45952</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45749</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43967,7 +43967,7 @@
         <v>45952</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45953</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44123,7 +44123,7 @@
         <v>45954</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>45957</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>46153</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45141</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>46153</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>44825</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45958</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>45958</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45959</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>45958</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>45390</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45961</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>45027</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45630</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45533</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45742</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45903</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>45986</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45472,7 +45472,7 @@
         <v>45966</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>45147</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>46153</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45691,7 +45691,7 @@
         <v>45191</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>45971</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45842,7 +45842,7 @@
         <v>45971</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>45974</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>46070</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45975</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45974</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45979</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45979</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45981</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>45981</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46509,7 +46509,7 @@
         <v>45980</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>45202</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         <v>45058</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>46157</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45987</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45987</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45986</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45001</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>46161</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45989</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45989</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>46161</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45988</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>45700</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47556,7 +47556,7 @@
         <v>45988</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         <v>45988</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47702,7 +47702,7 @@
         <v>45729</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45992</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45992</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>46161</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>44575</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48072,7 +48072,7 @@
         <v>44575</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45679</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>46162</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>44914</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45399</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48442,7 +48442,7 @@
         <v>46162</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48515,7 +48515,7 @@
         <v>45199</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48593,7 +48593,7 @@
         <v>45994</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>46163</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>46162</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45534</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45995</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>46163</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>46163</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49109,7 +49109,7 @@
         <v>44586</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>46001</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>45726</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49328,7 +49328,7 @@
         <v>45294</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45153</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45120</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49552,7 +49552,7 @@
         <v>45741</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>46001</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49698,7 +49698,7 @@
         <v>46001</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49771,7 +49771,7 @@
         <v>44776</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49844,7 +49844,7 @@
         <v>46002</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49917,7 +49917,7 @@
         <v>46003</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45355</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>46003</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>46003</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50219,7 +50219,7 @@
         <v>46164</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>46006</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50365,7 +50365,7 @@
         <v>46164</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>45891</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45499</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>46169</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45594</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>46010</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50818,7 +50818,7 @@
         <v>46168</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>46014</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45866</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>45933</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51120,7 +51120,7 @@
         <v>45922</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>45933</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51276,7 +51276,7 @@
         <v>45999</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45929</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>45968</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51510,7 +51510,7 @@
         <v>45979</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>45895</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45932</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51744,7 +51744,7 @@
         <v>45968</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>45915</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>46169</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>44924</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>46168</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>45470</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52192,7 +52192,7 @@
         <v>45474</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>45236</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52343,7 +52343,7 @@
         <v>45236</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>44895</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         <v>45335</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>45932</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45940</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>45985</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45086</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>46029</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>46031</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>46170</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>46031</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>45387</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>46035</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>45219</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>45202</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>46035</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>46034</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>46034</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53687,7 +53687,7 @@
         <v>46034</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>46174</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53838,7 +53838,7 @@
         <v>45686</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53911,7 +53911,7 @@
         <v>46036</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53984,7 +53984,7 @@
         <v>45078</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>44994</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54130,7 +54130,7 @@
         <v>46174</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45860</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>45856</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54359,7 +54359,7 @@
         <v>45922</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54432,7 +54432,7 @@
         <v>46171</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54510,7 +54510,7 @@
         <v>45638</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54583,7 +54583,7 @@
         <v>46041</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54656,7 +54656,7 @@
         <v>45008</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54729,7 +54729,7 @@
         <v>45060</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54802,7 +54802,7 @@
         <v>46043</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54875,7 +54875,7 @@
         <v>46043</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54948,7 +54948,7 @@
         <v>45170</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55021,7 +55021,7 @@
         <v>46174</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55099,7 +55099,7 @@
         <v>46174</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>46174</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         <v>45664</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
         <v>45169</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>46171</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55484,7 +55484,7 @@
         <v>46049</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55562,7 +55562,7 @@
         <v>45673</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55640,7 +55640,7 @@
         <v>45804</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55718,7 +55718,7 @@
         <v>46048</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         <v>44575</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55864,7 +55864,7 @@
         <v>46176</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55942,7 +55942,7 @@
         <v>45391</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         <v>46050</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>46175</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56171,7 +56171,7 @@
         <v>46085</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56244,7 +56244,7 @@
         <v>46051</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56317,7 +56317,7 @@
         <v>46175</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56395,7 +56395,7 @@
         <v>45539</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56473,7 +56473,7 @@
         <v>46175</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56551,7 +56551,7 @@
         <v>46055</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56629,7 +56629,7 @@
         <v>46052</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56702,7 +56702,7 @@
         <v>46052</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56775,7 +56775,7 @@
         <v>44740</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56848,7 +56848,7 @@
         <v>45678</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56921,7 +56921,7 @@
         <v>46055</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>46052</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>46177</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45631</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57223,7 +57223,7 @@
         <v>46057</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>45989</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>46105</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>46177</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>45561</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57598,7 +57598,7 @@
         <v>46063</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>44987</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57749,7 +57749,7 @@
         <v>45804</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>46083</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57895,7 +57895,7 @@
         <v>46065</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57968,7 +57968,7 @@
         <v>46066</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -58041,7 +58041,7 @@
         <v>45825</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>46182</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>46069</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58265,7 +58265,7 @@
         <v>46070</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>46070</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58421,7 +58421,7 @@
         <v>45040</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>45985</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>45170</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         <v>45653</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>46078</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>46079</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58859,7 +58859,7 @@
         <v>46079</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58932,7 +58932,7 @@
         <v>46079</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -59005,7 +59005,7 @@
         <v>46079</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>46079</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>46080</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59224,7 +59224,7 @@
         <v>46184</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59302,7 +59302,7 @@
         <v>46079</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59375,7 +59375,7 @@
         <v>46184</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>46080</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59526,7 +59526,7 @@
         <v>46083</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59599,7 +59599,7 @@
         <v>46083</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59672,7 +59672,7 @@
         <v>46083</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59750,7 +59750,7 @@
         <v>46185</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59828,7 +59828,7 @@
         <v>46083</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>46083</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59974,7 +59974,7 @@
         <v>46083</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -60047,7 +60047,7 @@
         <v>46085</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>46086</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60193,7 +60193,7 @@
         <v>46085</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>46086</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60344,7 +60344,7 @@
         <v>46188</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60417,7 +60417,7 @@
         <v>46188</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60490,7 +60490,7 @@
         <v>46188</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60563,7 +60563,7 @@
         <v>46090</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60641,7 +60641,7 @@
         <v>46092</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
         <v>46091</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60792,7 +60792,7 @@
         <v>46093</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60870,7 +60870,7 @@
         <v>46093</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60948,7 +60948,7 @@
         <v>46093</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -61026,7 +61026,7 @@
         <v>46093</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>45686</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61177,7 +61177,7 @@
         <v>46093</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61255,7 +61255,7 @@
         <v>46093</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61333,7 +61333,7 @@
         <v>46093</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61411,7 +61411,7 @@
         <v>46098</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61484,7 +61484,7 @@
         <v>46191</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61562,7 +61562,7 @@
         <v>46196</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61635,7 +61635,7 @@
         <v>46196</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61713,7 +61713,7 @@
         <v>45742</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61791,7 +61791,7 @@
         <v>46196</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61869,7 +61869,7 @@
         <v>46196</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>46104</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -62020,7 +62020,7 @@
         <v>46104</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -62098,7 +62098,7 @@
         <v>46104</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62171,7 +62171,7 @@
         <v>46104</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62244,7 +62244,7 @@
         <v>45233</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62317,7 +62317,7 @@
         <v>46197</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>46198</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62468,7 +62468,7 @@
         <v>46198</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62546,7 +62546,7 @@
         <v>45909</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62619,7 +62619,7 @@
         <v>46105</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>46105</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62765,7 +62765,7 @@
         <v>44823</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62838,7 +62838,7 @@
         <v>46198</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62911,7 +62911,7 @@
         <v>45441</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62984,7 +62984,7 @@
         <v>46197</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -63057,7 +63057,7 @@
         <v>45450</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63130,7 +63130,7 @@
         <v>46197</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63208,7 +63208,7 @@
         <v>46197</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63286,7 +63286,7 @@
         <v>46197</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63359,7 +63359,7 @@
         <v>44874</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63432,7 +63432,7 @@
         <v>46199</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63510,7 +63510,7 @@
         <v>46200</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63588,7 +63588,7 @@
         <v>46244</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         <v>46199</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63744,7 +63744,7 @@
         <v>46111</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63822,7 +63822,7 @@
         <v>46045</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63900,7 +63900,7 @@
         <v>46114</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63973,7 +63973,7 @@
         <v>46120</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -64046,7 +64046,7 @@
         <v>45714</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64124,7 +64124,7 @@
         <v>45279</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64197,7 +64197,7 @@
         <v>46120</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64275,7 +64275,7 @@
         <v>46121</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>46125</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64426,7 +64426,7 @@
         <v>46125</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64499,7 +64499,7 @@
         <v>45355</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64572,7 +64572,7 @@
         <v>46127</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64650,7 +64650,7 @@
         <v>46127</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64728,7 +64728,7 @@
         <v>46127</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64806,7 +64806,7 @@
         <v>46128</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64884,7 +64884,7 @@
         <v>46245</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64962,7 +64962,7 @@
         <v>45548</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -65035,7 +65035,7 @@
         <v>46127</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65113,7 +65113,7 @@
         <v>46244</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65191,7 +65191,7 @@
         <v>46244</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65269,7 +65269,7 @@
         <v>46127</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65342,7 +65342,7 @@
         <v>46127</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65420,7 +65420,7 @@
         <v>46199</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65498,7 +65498,7 @@
         <v>45217</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65571,7 +65571,7 @@
         <v>45992</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65649,7 +65649,7 @@
         <v>45320</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65727,7 +65727,7 @@
         <v>46204</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65805,7 +65805,7 @@
         <v>45289</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65878,7 +65878,7 @@
         <v>44929</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65951,7 +65951,7 @@
         <v>46134</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -66029,7 +66029,7 @@
         <v>46135</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -66107,7 +66107,7 @@
         <v>46134</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66185,7 +66185,7 @@
         <v>45642</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66258,7 +66258,7 @@
         <v>46136</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66331,7 +66331,7 @@
         <v>44712</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66404,7 +66404,7 @@
         <v>46139</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66477,7 +66477,7 @@
         <v>46204</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66555,7 +66555,7 @@
         <v>46139</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66628,7 +66628,7 @@
         <v>45009</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66701,7 +66701,7 @@
         <v>46246</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66779,7 +66779,7 @@
         <v>46139</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66852,7 +66852,7 @@
         <v>45280</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66930,7 +66930,7 @@
         <v>45280</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -67008,7 +67008,7 @@
         <v>45166</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -67086,7 +67086,7 @@
         <v>46010</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67159,7 +67159,7 @@
         <v>46246</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67237,7 +67237,7 @@
         <v>46246</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67315,7 +67315,7 @@
         <v>46206</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67393,7 +67393,7 @@
         <v>46248</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67471,7 +67471,7 @@
         <v>44594</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67544,7 +67544,7 @@
         <v>45742</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>46248</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67700,7 +67700,7 @@
         <v>45171</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67773,7 +67773,7 @@
         <v>46205</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67851,7 +67851,7 @@
         <v>46206</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67929,7 +67929,7 @@
         <v>44564</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -68002,7 +68002,7 @@
         <v>46206</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -68080,7 +68080,7 @@
         <v>44575</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68153,7 +68153,7 @@
         <v>45231</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68226,7 +68226,7 @@
         <v>45685</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68299,7 +68299,7 @@
         <v>46246</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68372,7 +68372,7 @@
         <v>46252</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68445,7 +68445,7 @@
         <v>46253</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68518,7 +68518,7 @@
         <v>44974</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68591,7 +68591,7 @@
         <v>45751</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68664,7 +68664,7 @@
         <v>46253</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68742,7 +68742,7 @@
         <v>44610</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68815,7 +68815,7 @@
         <v>46254</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68888,7 +68888,7 @@
         <v>46255</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68961,7 +68961,7 @@
         <v>45327</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -69034,7 +69034,7 @@
         <v>46211</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69112,7 +69112,7 @@
         <v>46211</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69190,7 +69190,7 @@
         <v>46212</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69263,7 +69263,7 @@
         <v>46211</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69341,7 +69341,7 @@
         <v>46216</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69419,7 +69419,7 @@
         <v>46213</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69497,7 +69497,7 @@
         <v>46134</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69575,7 +69575,7 @@
         <v>44462</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69653,7 +69653,7 @@
         <v>46259</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69726,7 +69726,7 @@
         <v>45590</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69799,7 +69799,7 @@
         <v>46259</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69872,7 +69872,7 @@
         <v>46216</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69950,7 +69950,7 @@
         <v>45202</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -70023,7 +70023,7 @@
         <v>46261</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -70096,7 +70096,7 @@
         <v>46261</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70169,7 +70169,7 @@
         <v>46260</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70247,7 +70247,7 @@
         <v>46260</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70325,7 +70325,7 @@
         <v>45293</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70398,7 +70398,7 @@
         <v>45182</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70471,7 +70471,7 @@
         <v>46261</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70544,7 +70544,7 @@
         <v>45516</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70617,7 +70617,7 @@
         <v>45749</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70690,7 +70690,7 @@
         <v>45674</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70763,7 +70763,7 @@
         <v>46221</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70841,7 +70841,7 @@
         <v>46265</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70919,7 +70919,7 @@
         <v>45351</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70997,7 +70997,7 @@
         <v>46265</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -71075,7 +71075,7 @@
         <v>46265</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71153,7 +71153,7 @@
         <v>45289</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71226,7 +71226,7 @@
         <v>46262</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71304,7 +71304,7 @@
         <v>46265</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71382,7 +71382,7 @@
         <v>46262</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71455,7 +71455,7 @@
         <v>46262</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71528,7 +71528,7 @@
         <v>46262</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71606,7 +71606,7 @@
         <v>45771</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71684,7 +71684,7 @@
         <v>46266</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71762,7 +71762,7 @@
         <v>44907</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71835,7 +71835,7 @@
         <v>45198</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71913,7 +71913,7 @@
         <v>46268</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -71986,7 +71986,7 @@
         <v>45205</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -72059,7 +72059,7 @@
         <v>45638</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -72132,7 +72132,7 @@
         <v>45770</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -72210,7 +72210,7 @@
         <v>44998</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -72283,7 +72283,7 @@
         <v>46225</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -72361,7 +72361,7 @@
         <v>45756</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -72434,7 +72434,7 @@
         <v>45359</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -72507,7 +72507,7 @@
         <v>45779</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72585,7 +72585,7 @@
         <v>45780</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -72658,7 +72658,7 @@
         <v>45119</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -72731,7 +72731,7 @@
         <v>46232</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -72804,7 +72804,7 @@
         <v>46275</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -72877,7 +72877,7 @@
         <v>46274</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -72955,7 +72955,7 @@
         <v>45785</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -73033,7 +73033,7 @@
         <v>46216</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -73106,7 +73106,7 @@
         <v>46276</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -73179,7 +73179,7 @@
         <v>45582</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -73252,7 +73252,7 @@
         <v>46105</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -73325,7 +73325,7 @@
         <v>46276</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -73398,7 +73398,7 @@
         <v>46248</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -73471,7 +73471,7 @@
         <v>46279</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -73544,7 +73544,7 @@
         <v>46279</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73617,7 +73617,7 @@
         <v>45789</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -73695,7 +73695,7 @@
         <v>46238</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -73773,7 +73773,7 @@
         <v>46238</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -73851,7 +73851,7 @@
         <v>45789</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -73929,7 +73929,7 @@
         <v>45526</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -74002,7 +74002,7 @@
         <v>46276</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -74075,7 +74075,7 @@
         <v>46280</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -74148,7 +74148,7 @@
         <v>45790</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -74221,7 +74221,7 @@
         <v>46281</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -74294,7 +74294,7 @@
         <v>46280</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -74367,7 +74367,7 @@
         <v>45790</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -74445,7 +74445,7 @@
         <v>45790</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -74518,7 +74518,7 @@
         <v>46281</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74596,7 +74596,7 @@
         <v>45793</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -74674,7 +74674,7 @@
         <v>45795</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -74752,7 +74752,7 @@
         <v>46248</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -74825,7 +74825,7 @@
         <v>46282</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -74898,7 +74898,7 @@
         <v>46282</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -74971,7 +74971,7 @@
         <v>45795</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -75049,7 +75049,7 @@
         <v>46239</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -75122,7 +75122,7 @@
         <v>45794</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -75200,7 +75200,7 @@
         <v>46241</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -75273,7 +75273,7 @@
         <v>46241</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -75346,7 +75346,7 @@
         <v>45799</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -75424,7 +75424,7 @@
         <v>45799</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -75502,7 +75502,7 @@
         <v>45799</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75580,7 +75580,7 @@
         <v>45259</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75653,7 +75653,7 @@
         <v>45483</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -75726,7 +75726,7 @@
         <v>45441</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -75799,7 +75799,7 @@
         <v>45804</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -75877,7 +75877,7 @@
         <v>45804</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -75955,7 +75955,7 @@
         <v>44512</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -76028,7 +76028,7 @@
         <v>45804</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -76106,7 +76106,7 @@
         <v>45805</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -76179,7 +76179,7 @@
         <v>45806</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -76257,7 +76257,7 @@
         <v>45806</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -76335,7 +76335,7 @@
         <v>45523</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -76408,7 +76408,7 @@
         <v>45810</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -76486,7 +76486,7 @@
         <v>45811</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -76564,7 +76564,7 @@
         <v>45813</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76642,7 +76642,7 @@
         <v>45813</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -76720,7 +76720,7 @@
         <v>45812</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -76793,7 +76793,7 @@
         <v>45818</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -76871,7 +76871,7 @@
         <v>45818</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -76949,7 +76949,7 @@
         <v>45819</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -77027,7 +77027,7 @@
         <v>45818</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -77105,7 +77105,7 @@
         <v>45823</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -77183,7 +77183,7 @@
         <v>45824</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -77256,7 +77256,7 @@
         <v>45824</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -77329,7 +77329,7 @@
         <v>45823</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -77407,7 +77407,7 @@
         <v>45827</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -77485,7 +77485,7 @@
         <v>45826</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -77558,7 +77558,7 @@
         <v>45826</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77631,7 +77631,7 @@
         <v>45832</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77709,7 +77709,7 @@
         <v>45832</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -77787,7 +77787,7 @@
         <v>45835</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -77860,7 +77860,7 @@
         <v>45839</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -77933,7 +77933,7 @@
         <v>45819</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -78011,7 +78011,7 @@
         <v>45839</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -78084,7 +78084,7 @@
         <v>45842</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -78157,7 +78157,7 @@
         <v>45842</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -78230,7 +78230,7 @@
         <v>45845</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -78303,7 +78303,7 @@
         <v>45842</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -78376,7 +78376,7 @@
         <v>45845</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -78449,7 +78449,7 @@
         <v>45849</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -78527,7 +78527,7 @@
         <v>45853</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78600,7 +78600,7 @@
         <v>45854</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -78673,7 +78673,7 @@
         <v>45854</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -78746,7 +78746,7 @@
         <v>45859</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -78819,7 +78819,7 @@
         <v>45873</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -78892,7 +78892,7 @@
         <v>45875</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -78970,7 +78970,7 @@
         <v>45873</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -79048,7 +79048,7 @@
         <v>45873</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -79126,7 +79126,7 @@
         <v>45877</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -79204,7 +79204,7 @@
         <v>45481</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -79277,7 +79277,7 @@
         <v>45877</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -79355,7 +79355,7 @@
         <v>45882</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -79433,7 +79433,7 @@
         <v>45883</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -79511,7 +79511,7 @@
         <v>45883</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -79589,7 +79589,7 @@
         <v>45883</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -79667,7 +79667,7 @@
         <v>45882</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -79745,7 +79745,7 @@
         <v>45463</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -79818,7 +79818,7 @@
         <v>45390</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -79891,7 +79891,7 @@
         <v>45323</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -79969,7 +79969,7 @@
         <v>45372</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -80042,7 +80042,7 @@
         <v>45744</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -80115,7 +80115,7 @@
         <v>45748</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -80188,7 +80188,7 @@
         <v>45782</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -80261,7 +80261,7 @@
         <v>46146</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -601,7 +601,7 @@
         <v>45954</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45110</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45419</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45586</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45376</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46164</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>46254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46253</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46267</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45952</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>44966</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>45425</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>46164</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45751</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45939</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>46170</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>45979</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45323</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>45880</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>45422</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>45889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45679</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>46188</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>44490</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44853</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4618,7 +4618,7 @@
         <v>45804</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45519</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45819</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>46240</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>46253</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>45517</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>44966</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>45932</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45939</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45943</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>44953</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>45875</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>45813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>45412</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>45875</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>45813</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44966</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>45889</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45783</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>46205</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>45456</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>45804</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45999</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>45782</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45118</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45678</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>45897</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>46091</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>45940</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>45776</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45932</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44776</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45187</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>46164</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45517</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45936</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>44806</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>45813</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>45856</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>46195</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>45945</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>46177</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45412</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>45385</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>44806</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45944</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>46128</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>44602</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>46253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45233</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>45771</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>46237</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>44474</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44928</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>45936</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45994</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>44900</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>45450</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44806</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>44712</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>46045</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>45545</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>45875</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45834</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>45834</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>46029</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>44477</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>46178</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45772</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>46244</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>44607</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>44943</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>44503</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45985</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>45769</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45944</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45954</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>46127</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45811</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45209</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>46176</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44572</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>45236</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>46237</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>46237</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>46178</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>46262</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>44529</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>44860</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45015</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>44791</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>46049</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>46069</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45931</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45931</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45237</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>45954</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>45960</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45933</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45712</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45490</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45989</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>44875</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>46150</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>46153</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46064</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         <v>45608</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45470</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45868</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45877</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>46199</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>46198</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45478</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>46094</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>46204</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>46134</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>44473</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>46266</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>46258</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45736</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45818</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>46233</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>46241</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>46244</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>46289</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45555</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>44986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>44806</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>44978</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>45475</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45588</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45782</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>45643</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>45789</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>44860</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45016</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45118</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45016</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45904</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>46049</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>44826</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45434</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45533</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>46006</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45960</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>46006</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>46006</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21674,7 +21674,7 @@
         <v>44841</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45517</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45527</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45560</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>45909</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>45888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>46107</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>46112</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>45511</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>46134</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>46136</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45959</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>45196</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>46136</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>46139</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44529</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>45555</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>46153</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>46157</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45840</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45853</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45856</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45092</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>46182</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45384</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45439</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>46197</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45200</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>46199</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45594</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>46204</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>46253</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>46029</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>44477</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>44473</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45200</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45236</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>45511</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>46282</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45595</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>46244</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45384</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>46244</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44606</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45260</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>45615</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45517</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>45118</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44546</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>44586</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44575</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>44536</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>44579</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27271,7 +27271,7 @@
         <v>44834</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>44587</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>44529</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         <v>44839</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>44729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>44872</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>44564</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44536</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>44487</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>44573</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>44587</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44810</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>44698</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44530</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44615</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>44694</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>44575</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>44714</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44847</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>44648</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>44839</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44529</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44599</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44529</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44810</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>44594</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>44594</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>44795</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45280</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45327</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>45266</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45370</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>45217</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>45399</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>45450</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45426</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45289</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45387</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>45391</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45265</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>44853</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>44487</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45795</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45883</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45231</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45866</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>45933</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>45968</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30860,7 +30860,7 @@
         <v>45922</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45895</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45968</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45999</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45932</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>45933</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>45979</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>45929</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>45915</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>45279</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45795</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>44895</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45419</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>45794</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45932</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45940</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>46029</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45985</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45883</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>45484</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>45793</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>45476</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>45883</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45042</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45483</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45499</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>46034</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>45441</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>46031</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>46031</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>46034</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>45335</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>44575</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44575</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45548</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45483</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>45838</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>46035</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>46035</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>46036</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45888</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45890</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45799</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>44874</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34197,7 +34197,7 @@
         <v>45890</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>44564</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45799</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45860</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>45642</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45856</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45896</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>45294</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>45895</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34884,7 +34884,7 @@
         <v>45895</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>46041</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         <v>45895</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45799</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>44924</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>44909</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35337,7 +35337,7 @@
         <v>44909</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>44909</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>45898</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>45897</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>46043</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>45897</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>45259</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>46043</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>45897</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>44610</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>45898</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>46048</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>46049</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45903</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>46050</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36452,7 +36452,7 @@
         <v>45539</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>46052</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>46052</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>46052</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45664</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>45905</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>45905</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>45908</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>46051</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>46055</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37197,7 +37197,7 @@
         <v>46055</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>44512</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>45911</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>45804</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>46057</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>45911</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>45911</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45742</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37801,7 +37801,7 @@
         <v>45915</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45915</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>45915</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>45804</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>45119</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>45390</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>46063</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38327,7 +38327,7 @@
         <v>45917</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>45919</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>45919</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>46066</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>45922</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45919</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>46065</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>46070</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>46070</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>46069</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45804</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>45923</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>44594</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45806</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>44951</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>45009</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46079</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45930</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>46078</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>46079</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>46083</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>46083</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45930</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>46079</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>46079</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40202,7 +40202,7 @@
         <v>46083</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
         <v>46079</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40348,7 +40348,7 @@
         <v>46080</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40421,7 +40421,7 @@
         <v>46083</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>46083</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>46083</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45931</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>46079</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>46080</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>45806</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>45805</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45523</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>45586</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45931</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>46085</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>46085</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>46086</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>46086</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45933</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>46091</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>46090</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45810</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>44907</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>45359</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>46093</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>46092</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>46093</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>46093</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>46093</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>46093</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>44740</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42520,7 +42520,7 @@
         <v>45679</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>46093</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>46093</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45686</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>45943</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45911</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45943</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>45944</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>46098</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>45267</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>45426</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>44994</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43411,7 +43411,7 @@
         <v>45812</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45945</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43557,7 +43557,7 @@
         <v>45945</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45947</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43713,7 +43713,7 @@
         <v>45950</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43791,7 +43791,7 @@
         <v>46104</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>46105</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>45947</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>45950</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>46105</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45947</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45947</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>46104</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>46104</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>46104</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45952</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45952</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>45008</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45953</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>46111</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45954</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45953</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>46045</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45958</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45958</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45811</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>45957</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>45958</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45535,7 +45535,7 @@
         <v>45294</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45219</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>46114</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>45959</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>46120</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>46120</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>46121</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>44979</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>46125</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45961</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>46125</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46353,7 +46353,7 @@
         <v>44902</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>45966</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>46127</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>46127</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>46127</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45581</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>45001</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45813</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45813</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45971</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45971</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45974</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>46127</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47337,7 +47337,7 @@
         <v>46127</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45974</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>45818</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>46128</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45289</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>46127</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45356</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45355</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45147</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45818</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>45975</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45979</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45980</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>45992</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48389,7 +48389,7 @@
         <v>45979</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48467,7 +48467,7 @@
         <v>46134</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>45981</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>46134</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>45981</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>45712</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48852,7 +48852,7 @@
         <v>46136</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>46136</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49008,7 +49008,7 @@
         <v>46136</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>46136</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>45986</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>44929</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45455</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>45455</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>45987</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49524,7 +49524,7 @@
         <v>46136</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49602,7 +49602,7 @@
         <v>46136</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45988</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45987</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>46136</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49909,7 +49909,7 @@
         <v>46136</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>45988</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>45988</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>46135</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>45992</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>46136</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>45992</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>46136</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>46136</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>46136</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50664,7 +50664,7 @@
         <v>46136</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45989</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>45989</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50883,7 +50883,7 @@
         <v>46136</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>45729</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51034,7 +51034,7 @@
         <v>46136</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>46139</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>45995</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51253,7 +51253,7 @@
         <v>45741</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51326,7 +51326,7 @@
         <v>45170</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51399,7 +51399,7 @@
         <v>45183</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45701</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>45805</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>46002</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51696,7 +51696,7 @@
         <v>44776</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>45818</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51847,7 +51847,7 @@
         <v>44923</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>45653</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51993,7 +51993,7 @@
         <v>45786</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>46001</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45708</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52212,7 +52212,7 @@
         <v>46001</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>46001</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45625</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>46003</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>45078</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52582,7 +52582,7 @@
         <v>46139</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>46003</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>46003</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>46006</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>45891</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45327</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53035,7 +53035,7 @@
         <v>45815</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>45819</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53186,7 +53186,7 @@
         <v>46010</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>46139</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53332,7 +53332,7 @@
         <v>46139</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>46139</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>45771</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>46014</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53634,7 +53634,7 @@
         <v>46031</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53707,7 +53707,7 @@
         <v>46010</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45824</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>45595</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53926,7 +53926,7 @@
         <v>45824</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53999,7 +53999,7 @@
         <v>45823</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54077,7 +54077,7 @@
         <v>45823</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54155,7 +54155,7 @@
         <v>46139</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54228,7 +54228,7 @@
         <v>45205</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45670</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54379,7 +54379,7 @@
         <v>45826</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45208</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54525,7 +54525,7 @@
         <v>46139</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54598,7 +54598,7 @@
         <v>45539</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54676,7 +54676,7 @@
         <v>45826</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54749,7 +54749,7 @@
         <v>45996</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>45989</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54900,7 +54900,7 @@
         <v>46142</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54973,7 +54973,7 @@
         <v>46142</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55046,7 +55046,7 @@
         <v>45474</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55119,7 +55119,7 @@
         <v>45203</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55192,7 +55192,7 @@
         <v>45730</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55265,7 +55265,7 @@
         <v>46121</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55338,7 +55338,7 @@
         <v>46142</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55411,7 +55411,7 @@
         <v>46090</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55489,7 +55489,7 @@
         <v>45827</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>45714</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45812</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55718,7 +55718,7 @@
         <v>46146</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55791,7 +55791,7 @@
         <v>46146</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55864,7 +55864,7 @@
         <v>46146</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55937,7 +55937,7 @@
         <v>46146</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56010,7 +56010,7 @@
         <v>44825</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56083,7 +56083,7 @@
         <v>46147</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56156,7 +56156,7 @@
         <v>46148</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56229,7 +56229,7 @@
         <v>45832</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56307,7 +56307,7 @@
         <v>45832</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56385,7 +56385,7 @@
         <v>45986</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>44685</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56531,7 +56531,7 @@
         <v>46070</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>46153</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>45903</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56755,7 +56755,7 @@
         <v>45749</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56828,7 +56828,7 @@
         <v>46153</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56901,7 +56901,7 @@
         <v>45264</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56974,7 +56974,7 @@
         <v>46153</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57047,7 +57047,7 @@
         <v>45202</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57120,7 +57120,7 @@
         <v>46153</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57198,7 +57198,7 @@
         <v>46153</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>45060</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45441</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57417,7 +57417,7 @@
         <v>45835</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57490,7 +57490,7 @@
         <v>46157</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57563,7 +57563,7 @@
         <v>44837</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57636,7 +57636,7 @@
         <v>46161</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57714,7 +57714,7 @@
         <v>46162</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57787,7 +57787,7 @@
         <v>46161</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57865,7 +57865,7 @@
         <v>46161</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57943,7 +57943,7 @@
         <v>46162</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -58016,7 +58016,7 @@
         <v>46162</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>45839</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -58162,7 +58162,7 @@
         <v>45365</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -58235,7 +58235,7 @@
         <v>45595</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -58308,7 +58308,7 @@
         <v>45819</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -58386,7 +58386,7 @@
         <v>45258</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58459,7 +58459,7 @@
         <v>45839</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58532,7 +58532,7 @@
         <v>45526</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58605,7 +58605,7 @@
         <v>45842</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58678,7 +58678,7 @@
         <v>45131</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58756,7 +58756,7 @@
         <v>45842</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58829,7 +58829,7 @@
         <v>45842</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58902,7 +58902,7 @@
         <v>45845</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45845</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -59048,7 +59048,7 @@
         <v>46163</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45280</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -59194,7 +59194,7 @@
         <v>45280</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -59272,7 +59272,7 @@
         <v>46164</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>46164</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59418,7 +59418,7 @@
         <v>46163</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59491,7 +59491,7 @@
         <v>46163</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59564,7 +59564,7 @@
         <v>45407</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59642,7 +59642,7 @@
         <v>46168</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>45086</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59788,7 +59788,7 @@
         <v>45849</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59866,7 +59866,7 @@
         <v>44987</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59939,7 +59939,7 @@
         <v>45320</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -60017,7 +60017,7 @@
         <v>45854</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -60090,7 +60090,7 @@
         <v>45853</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -60163,7 +60163,7 @@
         <v>45854</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -60236,7 +60236,7 @@
         <v>46169</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -60314,7 +60314,7 @@
         <v>46169</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60387,7 +60387,7 @@
         <v>46168</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60460,7 +60460,7 @@
         <v>46170</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60538,7 +60538,7 @@
         <v>44903</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>46171</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60689,7 +60689,7 @@
         <v>46171</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60767,7 +60767,7 @@
         <v>45859</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60840,7 +60840,7 @@
         <v>45419</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60918,7 +60918,7 @@
         <v>45202</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60991,7 +60991,7 @@
         <v>46174</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>45922</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -61142,7 +61142,7 @@
         <v>46174</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -61215,7 +61215,7 @@
         <v>46174</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         <v>45804</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -61371,7 +61371,7 @@
         <v>46085</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61444,7 +61444,7 @@
         <v>46175</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>45686</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61595,7 +61595,7 @@
         <v>46034</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61668,7 +61668,7 @@
         <v>46175</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61746,7 +61746,7 @@
         <v>46175</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61824,7 +61824,7 @@
         <v>46174</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61902,7 +61902,7 @@
         <v>46174</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61980,7 +61980,7 @@
         <v>45804</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -62053,7 +62053,7 @@
         <v>45989</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -62126,7 +62126,7 @@
         <v>45141</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -62204,7 +62204,7 @@
         <v>46177</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -62277,7 +62277,7 @@
         <v>46083</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -62350,7 +62350,7 @@
         <v>46105</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62423,7 +62423,7 @@
         <v>46176</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62501,7 +62501,7 @@
         <v>45525</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62574,7 +62574,7 @@
         <v>46182</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62647,7 +62647,7 @@
         <v>45985</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62720,7 +62720,7 @@
         <v>45289</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62793,7 +62793,7 @@
         <v>45825</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62866,7 +62866,7 @@
         <v>45040</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62939,7 +62939,7 @@
         <v>45638</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -63012,7 +63012,7 @@
         <v>45120</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -63085,7 +63085,7 @@
         <v>45182</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>46185</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>46184</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -63314,7 +63314,7 @@
         <v>46184</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63392,7 +63392,7 @@
         <v>46188</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63465,7 +63465,7 @@
         <v>45533</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63538,7 +63538,7 @@
         <v>46188</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>46188</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>45873</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63757,7 +63757,7 @@
         <v>45873</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>46191</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63913,7 +63913,7 @@
         <v>45875</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63991,7 +63991,7 @@
         <v>45191</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -64069,7 +64069,7 @@
         <v>46197</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -64142,7 +64142,7 @@
         <v>46197</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -64215,7 +64215,7 @@
         <v>46197</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -64288,7 +64288,7 @@
         <v>45058</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64366,7 +64366,7 @@
         <v>45638</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>45590</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64512,7 +64512,7 @@
         <v>45877</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45670</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>45909</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>46196</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64814,7 +64814,7 @@
         <v>46196</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64887,7 +64887,7 @@
         <v>46196</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64965,7 +64965,7 @@
         <v>46196</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -65043,7 +65043,7 @@
         <v>46197</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -65121,7 +65121,7 @@
         <v>46197</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -65199,7 +65199,7 @@
         <v>45481</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>46198</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65350,7 +65350,7 @@
         <v>46199</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65428,7 +65428,7 @@
         <v>45877</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
         <v>45630</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>46200</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65657,7 +65657,7 @@
         <v>46199</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65735,7 +65735,7 @@
         <v>46198</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65808,7 +65808,7 @@
         <v>46199</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65886,7 +65886,7 @@
         <v>46198</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65964,7 +65964,7 @@
         <v>45882</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -66042,7 +66042,7 @@
         <v>45882</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45594</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -66193,7 +66193,7 @@
         <v>46204</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -66271,7 +66271,7 @@
         <v>45678</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -66344,7 +66344,7 @@
         <v>46204</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66422,7 +66422,7 @@
         <v>46205</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66500,7 +66500,7 @@
         <v>44606</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66573,7 +66573,7 @@
         <v>46206</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66651,7 +66651,7 @@
         <v>46206</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66729,7 +66729,7 @@
         <v>46252</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66802,7 +66802,7 @@
         <v>45611</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66880,7 +66880,7 @@
         <v>46206</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66958,7 +66958,7 @@
         <v>46211</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -67036,7 +67036,7 @@
         <v>45673</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -67114,7 +67114,7 @@
         <v>46253</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -67192,7 +67192,7 @@
         <v>46211</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -67270,7 +67270,7 @@
         <v>46254</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -67343,7 +67343,7 @@
         <v>46211</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67421,7 +67421,7 @@
         <v>46253</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67494,7 +67494,7 @@
         <v>46212</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67567,7 +67567,7 @@
         <v>46255</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67640,7 +67640,7 @@
         <v>45153</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67713,7 +67713,7 @@
         <v>46216</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67791,7 +67791,7 @@
         <v>46260</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67869,7 +67869,7 @@
         <v>46259</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67942,7 +67942,7 @@
         <v>46213</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -68020,7 +68020,7 @@
         <v>46216</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -68098,7 +68098,7 @@
         <v>46260</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -68176,7 +68176,7 @@
         <v>45198</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -68254,7 +68254,7 @@
         <v>44775</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -68332,7 +68332,7 @@
         <v>46259</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68405,7 +68405,7 @@
         <v>46261</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68478,7 +68478,7 @@
         <v>46262</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68551,7 +68551,7 @@
         <v>44712</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68624,7 +68624,7 @@
         <v>46261</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68697,7 +68697,7 @@
         <v>46261</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68770,7 +68770,7 @@
         <v>46262</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68848,7 +68848,7 @@
         <v>46262</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68921,7 +68921,7 @@
         <v>45217</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68994,7 +68994,7 @@
         <v>45233</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -69067,7 +69067,7 @@
         <v>45201</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -69145,7 +69145,7 @@
         <v>45170</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -69218,7 +69218,7 @@
         <v>45170</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -69291,7 +69291,7 @@
         <v>45169</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69369,7 +69369,7 @@
         <v>46265</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69447,7 +69447,7 @@
         <v>46265</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69525,7 +69525,7 @@
         <v>44740</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69598,7 +69598,7 @@
         <v>45278</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69671,7 +69671,7 @@
         <v>46221</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69749,7 +69749,7 @@
         <v>45166</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69827,7 +69827,7 @@
         <v>46265</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69905,7 +69905,7 @@
         <v>45770</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69983,7 +69983,7 @@
         <v>46265</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -70061,7 +70061,7 @@
         <v>45306</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -70134,7 +70134,7 @@
         <v>46266</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -70212,7 +70212,7 @@
         <v>46262</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -70290,7 +70290,7 @@
         <v>45534</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -70363,7 +70363,7 @@
         <v>45294</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70441,7 +70441,7 @@
         <v>46268</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70514,7 +70514,7 @@
         <v>46225</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70592,7 +70592,7 @@
         <v>44998</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70665,7 +70665,7 @@
         <v>45343</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70738,7 +70738,7 @@
         <v>45330</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70811,7 +70811,7 @@
         <v>45630</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70884,7 +70884,7 @@
         <v>45756</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70957,7 +70957,7 @@
         <v>46274</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -71035,7 +71035,7 @@
         <v>45050</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -71108,7 +71108,7 @@
         <v>45027</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -71181,7 +71181,7 @@
         <v>45351</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -71259,7 +71259,7 @@
         <v>45279</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -71332,7 +71332,7 @@
         <v>45268</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71405,7 +71405,7 @@
         <v>46276</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71478,7 +71478,7 @@
         <v>45293</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71551,7 +71551,7 @@
         <v>46232</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71624,7 +71624,7 @@
         <v>46275</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71697,7 +71697,7 @@
         <v>46276</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71770,7 +71770,7 @@
         <v>45749</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71843,7 +71843,7 @@
         <v>46279</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71916,7 +71916,7 @@
         <v>46216</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71989,7 +71989,7 @@
         <v>46280</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -72062,7 +72062,7 @@
         <v>46279</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -72135,7 +72135,7 @@
         <v>46105</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -72208,7 +72208,7 @@
         <v>46238</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -72286,7 +72286,7 @@
         <v>46281</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -72364,7 +72364,7 @@
         <v>46276</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -72437,7 +72437,7 @@
         <v>46280</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -72510,7 +72510,7 @@
         <v>46238</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -72588,7 +72588,7 @@
         <v>46281</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -72661,7 +72661,7 @@
         <v>46282</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -72734,7 +72734,7 @@
         <v>46282</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72807,7 +72807,7 @@
         <v>44974</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -72880,7 +72880,7 @@
         <v>46239</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -72953,7 +72953,7 @@
         <v>45631</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -73031,7 +73031,7 @@
         <v>45553</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -73104,7 +73104,7 @@
         <v>45470</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -73177,7 +73177,7 @@
         <v>44914</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -73250,7 +73250,7 @@
         <v>45390</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -73323,7 +73323,7 @@
         <v>45266</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -73396,7 +73396,7 @@
         <v>45266</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -73474,7 +73474,7 @@
         <v>45511</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -73547,7 +73547,7 @@
         <v>45548</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -73620,7 +73620,7 @@
         <v>45561</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -73698,7 +73698,7 @@
         <v>45742</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -73776,7 +73776,7 @@
         <v>46241</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73849,7 +73849,7 @@
         <v>46241</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -73922,7 +73922,7 @@
         <v>46245</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -74000,7 +74000,7 @@
         <v>45524</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -74073,7 +74073,7 @@
         <v>46287</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -74146,7 +74146,7 @@
         <v>44715</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -74219,7 +74219,7 @@
         <v>46244</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -74297,7 +74297,7 @@
         <v>46288</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -74375,7 +74375,7 @@
         <v>45583</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -74453,7 +74453,7 @@
         <v>46244</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -74531,7 +74531,7 @@
         <v>46244</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -74609,7 +74609,7 @@
         <v>45191</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -74687,7 +74687,7 @@
         <v>46246</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -74760,7 +74760,7 @@
         <v>45533</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74838,7 +74838,7 @@
         <v>46246</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -74916,7 +74916,7 @@
         <v>46246</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -74994,7 +74994,7 @@
         <v>46248</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -75067,7 +75067,7 @@
         <v>46248</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -75145,7 +75145,7 @@
         <v>45280</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -75223,7 +75223,7 @@
         <v>45280</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -75301,7 +75301,7 @@
         <v>44902</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -75374,7 +75374,7 @@
         <v>46246</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -75452,7 +75452,7 @@
         <v>44586</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -75525,7 +75525,7 @@
         <v>44712</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -75598,7 +75598,7 @@
         <v>46248</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -75676,7 +75676,7 @@
         <v>45236</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -75754,7 +75754,7 @@
         <v>45236</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75832,7 +75832,7 @@
         <v>46289</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75910,7 +75910,7 @@
         <v>46248</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -75983,7 +75983,7 @@
         <v>46289</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -76061,7 +76061,7 @@
         <v>45215</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -76134,7 +76134,7 @@
         <v>45674</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -76207,7 +76207,7 @@
         <v>45674</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -76280,7 +76280,7 @@
         <v>45171</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -76353,7 +76353,7 @@
         <v>44575</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -76426,7 +76426,7 @@
         <v>44575</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -76499,7 +76499,7 @@
         <v>45009</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -76572,7 +76572,7 @@
         <v>45636</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -76645,7 +76645,7 @@
         <v>45638</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -76718,7 +76718,7 @@
         <v>45351</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -76791,7 +76791,7 @@
         <v>45293</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76864,7 +76864,7 @@
         <v>45419</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -76937,7 +76937,7 @@
         <v>45231</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -77010,7 +77010,7 @@
         <v>45700</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -77083,7 +77083,7 @@
         <v>45063</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -77156,7 +77156,7 @@
         <v>45199</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -77234,7 +77234,7 @@
         <v>45082</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -77307,7 +77307,7 @@
         <v>45202</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -77380,7 +77380,7 @@
         <v>45532</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -77458,7 +77458,7 @@
         <v>44823</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -77531,7 +77531,7 @@
         <v>45355</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -77604,7 +77604,7 @@
         <v>45534</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -77682,7 +77682,7 @@
         <v>45387</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -77755,7 +77755,7 @@
         <v>45351</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77828,7 +77828,7 @@
         <v>45693</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77901,7 +77901,7 @@
         <v>45351</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -77979,7 +77979,7 @@
         <v>45568</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -78052,7 +78052,7 @@
         <v>45154</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -78125,7 +78125,7 @@
         <v>45749</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -78198,7 +78198,7 @@
         <v>45726</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -78271,7 +78271,7 @@
         <v>45751</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -78344,7 +78344,7 @@
         <v>45208</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -78417,7 +78417,7 @@
         <v>45743</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -78490,7 +78490,7 @@
         <v>45685</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -78563,7 +78563,7 @@
         <v>45516</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -78636,7 +78636,7 @@
         <v>45742</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -78714,7 +78714,7 @@
         <v>45219</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78787,7 +78787,7 @@
         <v>45359</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -78860,7 +78860,7 @@
         <v>45780</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -78933,7 +78933,7 @@
         <v>45779</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -79011,7 +79011,7 @@
         <v>45119</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -79084,7 +79084,7 @@
         <v>45785</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -79162,7 +79162,7 @@
         <v>45582</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -79235,7 +79235,7 @@
         <v>45789</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -79313,7 +79313,7 @@
         <v>45789</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -79391,7 +79391,7 @@
         <v>45790</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -79464,7 +79464,7 @@
         <v>45790</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -79542,7 +79542,7 @@
         <v>45790</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -79615,7 +79615,7 @@
         <v>45526</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -79688,7 +79688,7 @@
         <v>45463</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -79761,7 +79761,7 @@
         <v>45390</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -79834,7 +79834,7 @@
         <v>45323</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -79912,7 +79912,7 @@
         <v>45372</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -79985,7 +79985,7 @@
         <v>45744</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -80058,7 +80058,7 @@
         <v>45748</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -80131,7 +80131,7 @@
         <v>45782</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -80204,7 +80204,7 @@
         <v>46146</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -601,7 +601,7 @@
         <v>45954</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45110</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45419</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45586</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45376</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46254</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45952</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45469</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>46274</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45425</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45875</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>46164</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>45751</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45939</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>46170</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45979</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>45880</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45875</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>45323</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>45422</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44477</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>45679</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44490</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>44853</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45804</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>45519</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45819</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>46240</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>46253</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>45943</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>45517</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44953</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>45932</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45939</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45875</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>45813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>44966</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45804</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45412</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44966</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45889</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>46205</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>45783</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45456</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>45999</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45782</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>45118</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>45678</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>45897</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>46091</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>45940</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44776</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>45776</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         <v>45932</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45187</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>46164</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>45936</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>45944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>45517</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45412</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45856</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45813</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>46195</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45945</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>46177</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>44806</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44806</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>44602</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>46128</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45233</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>45385</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>46237</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45771</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>46253</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>44474</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44900</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>44806</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>45936</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>45994</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45450</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44928</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>44712</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>46045</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>44607</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44572</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>45545</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45834</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45834</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>44845</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44477</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>46178</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45772</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>46244</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>46029</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>44943</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>44503</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>45769</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>45985</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44529</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45944</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>45954</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>46127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>45811</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>46176</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45209</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>46178</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>46237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>46237</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>46262</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>45236</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44860</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45015</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>44791</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45588</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>46049</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45931</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>45931</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>46069</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45954</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45960</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>45712</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45490</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>45989</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45933</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45608</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>44978</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45736</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>46153</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>46150</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45868</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45475</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45877</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44806</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>46064</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>46198</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>46199</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>44875</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>46204</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>46094</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>46134</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>44473</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>46266</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>46233</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>45818</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>46244</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>46289</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>46294</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>46241</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>45555</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>45470</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>46258</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>45237</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44986</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45478</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45782</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45643</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45789</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>44860</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45016</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45118</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45016</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45904</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>46049</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44826</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45595</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45959</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45517</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>46006</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>46006</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45960</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>46006</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45200</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>45909</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>45434</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45092</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45511</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>46107</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>46112</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45439</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>46134</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45527</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>46136</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45840</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>45533</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45853</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45196</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>46139</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45856</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>46136</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45594</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45555</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>46153</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>46157</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>46182</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>46197</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>46204</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>46029</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>44529</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>44477</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>44473</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45517</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>44606</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45511</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45384</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>45200</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>46282</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>46244</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45236</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>46244</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>46294</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>46253</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>45560</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44841</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45384</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45260</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>45615</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45118</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>44546</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44586</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>44575</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>44536</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44579</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>44834</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44587</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>44529</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44839</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>44729</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44872</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>44564</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>44536</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>44487</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>44573</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>44587</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>44810</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>44698</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>44530</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>44615</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>44694</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>44575</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>44714</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>44847</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>44648</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44839</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>44529</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>44599</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>44529</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>44810</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44594</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>44594</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44795</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>45365</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45359</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45063</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45533</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44837</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30000,7 +30000,7 @@
         <v>45625</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45426</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45267</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45534</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45532</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45670</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45191</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45351</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45183</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>45419</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>45419</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45583</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30926,7 +30926,7 @@
         <v>45231</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30999,7 +30999,7 @@
         <v>45743</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>45278</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45280</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31223,7 +31223,7 @@
         <v>45789</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>45741</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>46001</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>46001</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45789</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45484</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>44776</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>46002</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>46003</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>46003</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>46003</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45526</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>46006</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>45891</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>45419</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>46010</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44951</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>45790</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>46014</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>45866</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>45933</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>45922</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>45638</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>45933</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45999</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>45929</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>45968</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>45979</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>45895</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33415,7 +33415,7 @@
         <v>45932</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45968</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45915</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>45888</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>45890</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>45890</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>45895</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>45895</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>45895</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45940</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45985</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45897</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>45790</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>46029</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>46031</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>45896</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45897</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45790</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45897</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>46031</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>45170</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>44923</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45898</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>46035</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>45511</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45898</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>46035</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>46034</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>46034</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>45903</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>46036</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>44712</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45905</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>45905</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>45860</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>45856</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>44909</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>44909</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>45908</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>46041</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45203</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>46043</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45258</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>46043</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>45793</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45911</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45911</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45795</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>45911</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>45795</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>45794</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>45915</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>45915</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37404,7 +37404,7 @@
         <v>46049</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>44487</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>45915</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>44740</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45268</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45387</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>46048</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45799</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45799</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>45799</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         <v>46050</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38227,7 +38227,7 @@
         <v>45259</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38300,7 +38300,7 @@
         <v>45483</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45441</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>45343</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>45919</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38597,7 +38597,7 @@
         <v>45919</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>46051</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38748,7 +38748,7 @@
         <v>45804</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>45804</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>45919</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>44512</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>45804</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39128,7 +39128,7 @@
         <v>45805</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>46055</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39279,7 +39279,7 @@
         <v>45806</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39357,7 +39357,7 @@
         <v>45806</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         <v>45523</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>46052</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39581,7 +39581,7 @@
         <v>46052</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>46055</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45923</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45922</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>46052</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>45810</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>46057</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45426</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>45930</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>45931</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>45930</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40409,7 +40409,7 @@
         <v>45931</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40482,7 +40482,7 @@
         <v>46063</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>45611</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>45933</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>45701</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>46065</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>46066</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45119</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>46069</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>46070</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>46070</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>45811</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41315,7 +41315,7 @@
         <v>45943</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>45943</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41461,7 +41461,7 @@
         <v>45568</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45944</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45911</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45945</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45539</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>45947</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>45945</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>46078</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42060,7 +42060,7 @@
         <v>45947</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>45947</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>45947</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>46079</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46079</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>45950</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>46079</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>45370</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>46079</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>46079</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>46080</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45950</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42961,7 +42961,7 @@
         <v>46079</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45813</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>46080</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>45953</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>45952</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>46083</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>46083</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
         <v>46083</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45952</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>45953</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43711,7 +43711,7 @@
         <v>46083</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>46083</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>46083</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>45954</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -44008,7 +44008,7 @@
         <v>45957</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>44715</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>46085</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>46086</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44300,7 +44300,7 @@
         <v>46085</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>46086</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45813</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45958</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>45958</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45812</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45959</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45958</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>46090</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45961</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45289</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>46092</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>46093</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>45279</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>46093</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45131</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>46093</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>46093</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>45686</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45820,7 +45820,7 @@
         <v>46093</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>46093</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45976,7 +45976,7 @@
         <v>45966</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -46049,7 +46049,7 @@
         <v>46093</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>46098</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45971</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45356</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>45009</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45306</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>45971</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46565,7 +46565,7 @@
         <v>45548</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46638,7 +46638,7 @@
         <v>45708</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>46104</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>46104</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>46104</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>45974</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>46104</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>45975</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45974</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45818</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45082</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47378,7 +47378,7 @@
         <v>46105</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>45818</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>46105</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>45630</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47675,7 +47675,7 @@
         <v>45819</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47753,7 +47753,7 @@
         <v>45979</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47831,7 +47831,7 @@
         <v>45979</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45818</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45981</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45981</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48133,7 +48133,7 @@
         <v>45980</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45154</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>46111</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>46045</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48440,7 +48440,7 @@
         <v>45987</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48513,7 +48513,7 @@
         <v>46114</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>45712</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45526</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45987</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48815,7 +48815,7 @@
         <v>45823</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         <v>45986</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>45989</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45989</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>46120</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>45824</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45749</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>45824</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49404,7 +49404,7 @@
         <v>45476</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45988</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>46120</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49628,7 +49628,7 @@
         <v>45988</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49701,7 +49701,7 @@
         <v>45988</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45992</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45586</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49920,7 +49920,7 @@
         <v>45823</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>45992</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>46121</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>46125</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>46125</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45995</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50368,7 +50368,7 @@
         <v>45355</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50441,7 +50441,7 @@
         <v>46127</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50519,7 +50519,7 @@
         <v>46127</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>46127</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>46128</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45670</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45525</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50899,7 +50899,7 @@
         <v>46127</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50977,7 +50977,7 @@
         <v>45827</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>46001</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>46127</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51201,7 +51201,7 @@
         <v>45826</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>45826</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51347,7 +51347,7 @@
         <v>45294</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>46127</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>44853</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>44909</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45992</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51727,7 +51727,7 @@
         <v>45832</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>45832</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45289</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51956,7 +51956,7 @@
         <v>45201</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>45390</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>45217</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>44929</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52253,7 +52253,7 @@
         <v>45294</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52331,7 +52331,7 @@
         <v>46134</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45581</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52487,7 +52487,7 @@
         <v>45293</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>46135</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52638,7 +52638,7 @@
         <v>46134</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>45835</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>45455</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45455</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52935,7 +52935,7 @@
         <v>46136</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -53008,7 +53008,7 @@
         <v>45266</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53081,7 +53081,7 @@
         <v>46139</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53154,7 +53154,7 @@
         <v>45839</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53227,7 +53227,7 @@
         <v>45819</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53305,7 +53305,7 @@
         <v>45839</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53378,7 +53378,7 @@
         <v>46139</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53451,7 +53451,7 @@
         <v>46139</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53524,7 +53524,7 @@
         <v>46010</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53597,7 +53597,7 @@
         <v>45693</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53670,7 +53670,7 @@
         <v>45483</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>46139</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>44903</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45842</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>46031</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54040,7 +54040,7 @@
         <v>45842</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54113,7 +54113,7 @@
         <v>45351</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45845</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54259,7 +54259,7 @@
         <v>45842</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54332,7 +54332,7 @@
         <v>45595</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54405,7 +54405,7 @@
         <v>45845</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>46136</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>46136</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54634,7 +54634,7 @@
         <v>45786</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45849</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54785,7 +54785,7 @@
         <v>45264</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54858,7 +54858,7 @@
         <v>45266</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>45266</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>44902</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>46136</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55160,7 +55160,7 @@
         <v>46136</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>46139</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>45853</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>45215</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55462,7 +55462,7 @@
         <v>44902</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55535,7 +55535,7 @@
         <v>44606</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55608,7 +55608,7 @@
         <v>46136</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55681,7 +55681,7 @@
         <v>45854</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         <v>46136</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55832,7 +55832,7 @@
         <v>45815</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>44775</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55983,7 +55983,7 @@
         <v>46139</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45327</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56129,7 +56129,7 @@
         <v>46136</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56207,7 +56207,7 @@
         <v>45854</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>45407</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56358,7 +56358,7 @@
         <v>46136</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>46136</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>46136</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56587,7 +56587,7 @@
         <v>46136</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56665,7 +56665,7 @@
         <v>46136</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56743,7 +56743,7 @@
         <v>45351</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56816,7 +56816,7 @@
         <v>45265</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45553</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56962,7 +56962,7 @@
         <v>45219</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57035,7 +57035,7 @@
         <v>46136</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>46139</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57181,7 +57181,7 @@
         <v>44685</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57254,7 +57254,7 @@
         <v>46136</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57332,7 +57332,7 @@
         <v>45859</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57405,7 +57405,7 @@
         <v>45805</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57478,7 +57478,7 @@
         <v>45989</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57551,7 +57551,7 @@
         <v>45996</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45812</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>45730</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57775,7 +57775,7 @@
         <v>45208</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57848,7 +57848,7 @@
         <v>45208</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57921,7 +57921,7 @@
         <v>45674</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57994,7 +57994,7 @@
         <v>45595</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -58067,7 +58067,7 @@
         <v>45524</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -58140,7 +58140,7 @@
         <v>45050</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>44979</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>46090</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -58364,7 +58364,7 @@
         <v>45280</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>45280</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -58515,7 +58515,7 @@
         <v>45636</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>46142</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>46121</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>46142</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>46142</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58880,7 +58880,7 @@
         <v>46146</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58953,7 +58953,7 @@
         <v>46146</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -59026,7 +59026,7 @@
         <v>46146</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -59099,7 +59099,7 @@
         <v>46147</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -59172,7 +59172,7 @@
         <v>45873</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -59245,7 +59245,7 @@
         <v>45330</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -59318,7 +59318,7 @@
         <v>45749</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -59391,7 +59391,7 @@
         <v>46146</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -59464,7 +59464,7 @@
         <v>45141</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59542,7 +59542,7 @@
         <v>44825</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59615,7 +59615,7 @@
         <v>46148</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59688,7 +59688,7 @@
         <v>46153</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59761,7 +59761,7 @@
         <v>46153</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59839,7 +59839,7 @@
         <v>46153</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59912,7 +59912,7 @@
         <v>46153</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59985,7 +59985,7 @@
         <v>45390</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -60058,7 +60058,7 @@
         <v>45027</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -60131,7 +60131,7 @@
         <v>45630</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -60204,7 +60204,7 @@
         <v>45903</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -60282,7 +60282,7 @@
         <v>45533</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -60355,7 +60355,7 @@
         <v>45986</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -60428,7 +60428,7 @@
         <v>46153</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60501,7 +60501,7 @@
         <v>46070</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60574,7 +60574,7 @@
         <v>45742</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60652,7 +60652,7 @@
         <v>45875</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         <v>45202</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>45147</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60876,7 +60876,7 @@
         <v>45191</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60954,7 +60954,7 @@
         <v>46157</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -61027,7 +61027,7 @@
         <v>46161</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -61105,7 +61105,7 @@
         <v>46161</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>46161</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -61261,7 +61261,7 @@
         <v>45873</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -61339,7 +61339,7 @@
         <v>45877</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -61417,7 +61417,7 @@
         <v>46162</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -61490,7 +61490,7 @@
         <v>46162</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61563,7 +61563,7 @@
         <v>46163</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>46162</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61709,7 +61709,7 @@
         <v>46163</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>46163</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61855,7 +61855,7 @@
         <v>45481</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61928,7 +61928,7 @@
         <v>45877</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -62006,7 +62006,7 @@
         <v>46164</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -62079,7 +62079,7 @@
         <v>46164</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -62152,7 +62152,7 @@
         <v>45058</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>46169</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -62308,7 +62308,7 @@
         <v>46168</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>46169</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>46168</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62527,7 +62527,7 @@
         <v>46170</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45001</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62678,7 +62678,7 @@
         <v>45202</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>46034</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62824,7 +62824,7 @@
         <v>46174</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45686</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62975,7 +62975,7 @@
         <v>46174</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -63048,7 +63048,7 @@
         <v>45922</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -63121,7 +63121,7 @@
         <v>46171</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -63199,7 +63199,7 @@
         <v>45700</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -63272,7 +63272,7 @@
         <v>45882</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>45729</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -63423,7 +63423,7 @@
         <v>45883</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63501,7 +63501,7 @@
         <v>46174</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63579,7 +63579,7 @@
         <v>46174</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63657,7 +63657,7 @@
         <v>46174</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63735,7 +63735,7 @@
         <v>45883</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63813,7 +63813,7 @@
         <v>45883</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63891,7 +63891,7 @@
         <v>46171</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63969,7 +63969,7 @@
         <v>45882</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -64047,7 +64047,7 @@
         <v>45804</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -64125,7 +64125,7 @@
         <v>46176</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -64203,7 +64203,7 @@
         <v>46175</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -64281,7 +64281,7 @@
         <v>46085</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -64354,7 +64354,7 @@
         <v>46175</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>46175</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64510,7 +64510,7 @@
         <v>45042</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64583,7 +64583,7 @@
         <v>46177</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64656,7 +64656,7 @@
         <v>45989</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64729,7 +64729,7 @@
         <v>46105</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64802,7 +64802,7 @@
         <v>45838</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64880,7 +64880,7 @@
         <v>44575</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64953,7 +64953,7 @@
         <v>44575</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -65026,7 +65026,7 @@
         <v>45679</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -65099,7 +65099,7 @@
         <v>44914</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -65172,7 +65172,7 @@
         <v>45399</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -65250,7 +65250,7 @@
         <v>45804</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -65323,7 +65323,7 @@
         <v>46083</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -65396,7 +65396,7 @@
         <v>45199</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65474,7 +65474,7 @@
         <v>45825</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65547,7 +65547,7 @@
         <v>46182</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65620,7 +65620,7 @@
         <v>45040</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65693,7 +65693,7 @@
         <v>45985</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65766,7 +65766,7 @@
         <v>45534</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65839,7 +65839,7 @@
         <v>46184</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65917,7 +65917,7 @@
         <v>46184</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65995,7 +65995,7 @@
         <v>46185</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -66073,7 +66073,7 @@
         <v>44586</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -66146,7 +66146,7 @@
         <v>46188</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -66219,7 +66219,7 @@
         <v>46188</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -66292,7 +66292,7 @@
         <v>45726</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -66365,7 +66365,7 @@
         <v>45294</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -66443,7 +66443,7 @@
         <v>45153</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66516,7 +66516,7 @@
         <v>46188</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66589,7 +66589,7 @@
         <v>45120</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66662,7 +66662,7 @@
         <v>45355</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66735,7 +66735,7 @@
         <v>45499</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66813,7 +66813,7 @@
         <v>46191</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66891,7 +66891,7 @@
         <v>46196</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66964,7 +66964,7 @@
         <v>46196</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -67042,7 +67042,7 @@
         <v>45594</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -67115,7 +67115,7 @@
         <v>46196</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -67193,7 +67193,7 @@
         <v>46196</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -67271,7 +67271,7 @@
         <v>46197</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -67344,7 +67344,7 @@
         <v>46198</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -67422,7 +67422,7 @@
         <v>46198</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67500,7 +67500,7 @@
         <v>45909</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67573,7 +67573,7 @@
         <v>46198</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67646,7 +67646,7 @@
         <v>46197</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67719,7 +67719,7 @@
         <v>46197</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67797,7 +67797,7 @@
         <v>46197</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67875,7 +67875,7 @@
         <v>44924</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67948,7 +67948,7 @@
         <v>46197</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -68021,7 +68021,7 @@
         <v>46199</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -68099,7 +68099,7 @@
         <v>46200</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -68177,7 +68177,7 @@
         <v>46199</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -68255,7 +68255,7 @@
         <v>45470</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -68328,7 +68328,7 @@
         <v>45474</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -68401,7 +68401,7 @@
         <v>45236</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68479,7 +68479,7 @@
         <v>45236</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68557,7 +68557,7 @@
         <v>44895</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68630,7 +68630,7 @@
         <v>46199</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68708,7 +68708,7 @@
         <v>45335</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68786,7 +68786,7 @@
         <v>45086</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68859,7 +68859,7 @@
         <v>46204</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68937,7 +68937,7 @@
         <v>46204</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -69015,7 +69015,7 @@
         <v>45387</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -69088,7 +69088,7 @@
         <v>45219</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -69161,7 +69161,7 @@
         <v>46206</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -69239,7 +69239,7 @@
         <v>45078</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -69312,7 +69312,7 @@
         <v>46205</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -69390,7 +69390,7 @@
         <v>46206</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69468,7 +69468,7 @@
         <v>44994</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69541,7 +69541,7 @@
         <v>46206</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69619,7 +69619,7 @@
         <v>45638</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69692,7 +69692,7 @@
         <v>45008</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69765,7 +69765,7 @@
         <v>45060</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69838,7 +69838,7 @@
         <v>45170</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69911,7 +69911,7 @@
         <v>46211</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69989,7 +69989,7 @@
         <v>46211</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -70067,7 +70067,7 @@
         <v>46212</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -70140,7 +70140,7 @@
         <v>46211</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -70218,7 +70218,7 @@
         <v>45664</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -70291,7 +70291,7 @@
         <v>45169</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -70369,7 +70369,7 @@
         <v>46216</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -70447,7 +70447,7 @@
         <v>46213</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70525,7 +70525,7 @@
         <v>46259</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70598,7 +70598,7 @@
         <v>46259</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70671,7 +70671,7 @@
         <v>46216</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70749,7 +70749,7 @@
         <v>45673</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70827,7 +70827,7 @@
         <v>44575</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70900,7 +70900,7 @@
         <v>45391</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70978,7 +70978,7 @@
         <v>46261</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -71051,7 +71051,7 @@
         <v>46261</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -71124,7 +71124,7 @@
         <v>46260</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -71202,7 +71202,7 @@
         <v>46260</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -71280,7 +71280,7 @@
         <v>45539</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -71358,7 +71358,7 @@
         <v>44740</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -71431,7 +71431,7 @@
         <v>45678</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71504,7 +71504,7 @@
         <v>46261</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71577,7 +71577,7 @@
         <v>45631</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71655,7 +71655,7 @@
         <v>46221</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71733,7 +71733,7 @@
         <v>46265</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71811,7 +71811,7 @@
         <v>46265</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71889,7 +71889,7 @@
         <v>46265</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71967,7 +71967,7 @@
         <v>46262</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -72045,7 +72045,7 @@
         <v>46265</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -72123,7 +72123,7 @@
         <v>46262</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -72196,7 +72196,7 @@
         <v>46262</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -72269,7 +72269,7 @@
         <v>46262</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -72347,7 +72347,7 @@
         <v>45561</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -72425,7 +72425,7 @@
         <v>44987</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -72498,7 +72498,7 @@
         <v>46266</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -72576,7 +72576,7 @@
         <v>46268</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -72649,7 +72649,7 @@
         <v>44998</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -72722,7 +72722,7 @@
         <v>45170</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -72795,7 +72795,7 @@
         <v>46225</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -72873,7 +72873,7 @@
         <v>45756</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72946,7 +72946,7 @@
         <v>45653</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -73019,7 +73019,7 @@
         <v>46232</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -73092,7 +73092,7 @@
         <v>46275</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -73165,7 +73165,7 @@
         <v>46216</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -73238,7 +73238,7 @@
         <v>46276</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -73311,7 +73311,7 @@
         <v>46105</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -73384,7 +73384,7 @@
         <v>46276</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -73457,7 +73457,7 @@
         <v>46279</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -73530,7 +73530,7 @@
         <v>46279</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -73603,7 +73603,7 @@
         <v>46238</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -73681,7 +73681,7 @@
         <v>46238</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -73759,7 +73759,7 @@
         <v>46276</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -73832,7 +73832,7 @@
         <v>46280</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -73905,7 +73905,7 @@
         <v>46281</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73978,7 +73978,7 @@
         <v>46280</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -74051,7 +74051,7 @@
         <v>46281</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -74129,7 +74129,7 @@
         <v>46282</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -74202,7 +74202,7 @@
         <v>46282</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -74275,7 +74275,7 @@
         <v>46239</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -74348,7 +74348,7 @@
         <v>45742</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -74426,7 +74426,7 @@
         <v>45233</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -74499,7 +74499,7 @@
         <v>46287</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -74572,7 +74572,7 @@
         <v>46241</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -74645,7 +74645,7 @@
         <v>44823</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -74718,7 +74718,7 @@
         <v>45441</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -74791,7 +74791,7 @@
         <v>46244</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -74869,7 +74869,7 @@
         <v>46244</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74947,7 +74947,7 @@
         <v>45450</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -75020,7 +75020,7 @@
         <v>46244</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -75098,7 +75098,7 @@
         <v>44874</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -75171,7 +75171,7 @@
         <v>46241</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -75244,7 +75244,7 @@
         <v>46289</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -75322,7 +75322,7 @@
         <v>46246</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -75400,7 +75400,7 @@
         <v>46246</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -75478,7 +75478,7 @@
         <v>46245</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -75556,7 +75556,7 @@
         <v>46246</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -75629,7 +75629,7 @@
         <v>46288</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -75707,7 +75707,7 @@
         <v>45714</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -75785,7 +75785,7 @@
         <v>45279</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -75858,7 +75858,7 @@
         <v>46289</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75936,7 +75936,7 @@
         <v>46246</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -76014,7 +76014,7 @@
         <v>45917</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -76087,7 +76087,7 @@
         <v>46248</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -76160,7 +76160,7 @@
         <v>45548</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -76233,7 +76233,7 @@
         <v>45217</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -76306,7 +76306,7 @@
         <v>46248</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -76384,7 +76384,7 @@
         <v>45320</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -76462,7 +76462,7 @@
         <v>46248</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -76540,7 +76540,7 @@
         <v>45932</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -76618,7 +76618,7 @@
         <v>46287</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -76691,7 +76691,7 @@
         <v>46294</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -76764,7 +76764,7 @@
         <v>45642</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -76837,7 +76837,7 @@
         <v>44712</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -76910,7 +76910,7 @@
         <v>46252</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76983,7 +76983,7 @@
         <v>45009</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -77056,7 +77056,7 @@
         <v>45280</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -77134,7 +77134,7 @@
         <v>45280</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -77212,7 +77212,7 @@
         <v>45166</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -77290,7 +77290,7 @@
         <v>46248</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -77363,7 +77363,7 @@
         <v>46294</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -77436,7 +77436,7 @@
         <v>46297</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -77514,7 +77514,7 @@
         <v>46254</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -77587,7 +77587,7 @@
         <v>44594</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -77660,7 +77660,7 @@
         <v>45742</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -77738,7 +77738,7 @@
         <v>46253</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -77811,7 +77811,7 @@
         <v>46296</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -77889,7 +77889,7 @@
         <v>46297</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77962,7 +77962,7 @@
         <v>46297</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -78035,7 +78035,7 @@
         <v>46255</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -78108,7 +78108,7 @@
         <v>46253</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -78186,7 +78186,7 @@
         <v>45171</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -78259,7 +78259,7 @@
         <v>44564</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -78332,7 +78332,7 @@
         <v>44575</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -78405,7 +78405,7 @@
         <v>45231</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -78478,7 +78478,7 @@
         <v>45685</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -78551,7 +78551,7 @@
         <v>44974</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -78624,7 +78624,7 @@
         <v>45751</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -78697,7 +78697,7 @@
         <v>44610</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -78770,7 +78770,7 @@
         <v>45327</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -78843,7 +78843,7 @@
         <v>45590</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78916,7 +78916,7 @@
         <v>45202</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -78989,7 +78989,7 @@
         <v>45293</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -79062,7 +79062,7 @@
         <v>45182</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -79135,7 +79135,7 @@
         <v>45516</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -79208,7 +79208,7 @@
         <v>45749</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -79281,7 +79281,7 @@
         <v>45674</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -79354,7 +79354,7 @@
         <v>45351</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -79432,7 +79432,7 @@
         <v>45289</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -79505,7 +79505,7 @@
         <v>45771</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -79583,7 +79583,7 @@
         <v>44907</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -79656,7 +79656,7 @@
         <v>45198</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -79734,7 +79734,7 @@
         <v>45205</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -79807,7 +79807,7 @@
         <v>45638</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -79880,7 +79880,7 @@
         <v>45770</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -79958,7 +79958,7 @@
         <v>45359</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -80031,7 +80031,7 @@
         <v>45779</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -80109,7 +80109,7 @@
         <v>45780</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -80182,7 +80182,7 @@
         <v>45119</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -80255,7 +80255,7 @@
         <v>45785</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -80333,7 +80333,7 @@
         <v>45582</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -80406,7 +80406,7 @@
         <v>45463</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -80479,7 +80479,7 @@
         <v>45390</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -80552,7 +80552,7 @@
         <v>45323</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -80630,7 +80630,7 @@
         <v>45372</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -80703,7 +80703,7 @@
         <v>45744</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -80776,7 +80776,7 @@
         <v>45748</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -80849,7 +80849,7 @@
         <v>45782</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -80922,7 +80922,7 @@
         <v>46146</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -601,7 +601,7 @@
         <v>45954</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45110</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45419</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45586</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45376</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>45545</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46254</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>46164</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>46309</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>45952</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>45469</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>46274</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>44966</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>45875</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>46164</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45425</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>45939</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>46170</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         <v>45751</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>46310</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>45875</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45979</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>45880</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>46188</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>45422</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>45889</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>45679</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>46301</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44490</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44853</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>45519</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46240</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>46253</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>45804</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>45819</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>45943</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>45517</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44953</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>45875</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>45932</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>45939</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44966</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>45813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>45813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>45412</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44966</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>45889</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>46205</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>45783</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45804</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>45456</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>45999</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>46289</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45782</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>45118</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>46091</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45940</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>46301</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>45678</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>46268</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44776</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>45932</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>45187</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>46164</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>45776</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45936</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>45412</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>45944</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45813</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>45517</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>46195</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45945</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>44806</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>46177</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>45856</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>44806</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>44602</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>45233</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>46128</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>45385</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>46237</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>46253</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>45771</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>44900</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44806</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45936</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>45994</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45450</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44928</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44712</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>44607</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>44572</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>44845</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>46045</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45545</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>46178</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>46244</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45772</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>46029</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45834</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45834</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>44943</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>44503</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>44529</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45769</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45944</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45954</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45985</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>46176</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>45209</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>45236</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>46178</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>46237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>46237</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>46262</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>45811</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>44860</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>45015</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44791</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45588</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45712</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>45904</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>45608</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45931</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45931</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>46153</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>46150</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>44978</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>45736</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>45954</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45960</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>45490</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45989</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45475</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>44806</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>46064</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>46049</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>46069</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>44875</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>46198</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>46199</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45933</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>46204</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>46094</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>46134</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>46233</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45555</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45470</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>46244</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>46289</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>46246</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>45237</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>44986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>46294</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>46241</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>46258</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45478</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45782</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45643</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45789</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45818</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>46266</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45868</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45877</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>44860</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>45016</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>45118</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45016</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45904</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>46049</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         <v>44826</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45595</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45200</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45434</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>45092</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>45511</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45439</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>46139</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>46136</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>45527</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45533</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45555</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
         <v>46153</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>45196</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>46157</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45594</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45959</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>46006</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>46006</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
         <v>45960</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>46006</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>46182</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45909</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>44529</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45888</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>46197</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>46107</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>46112</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45517</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>44606</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>46204</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>46134</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>46136</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45384</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45200</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25259,7 +25259,7 @@
         <v>46029</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45236</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45511</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45560</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46282</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>46244</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46244</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44841</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45384</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>46294</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>46253</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45260</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45615</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>45517</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45840</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>45853</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45856</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45118</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>44546</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>44586</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>44575</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>44536</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>44579</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>44834</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>44587</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>44529</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>44839</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>44729</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44872</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44564</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>44536</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44487</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44573</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>44587</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>44810</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>44698</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>44530</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44615</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44694</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>44575</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>44714</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44847</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>44648</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44839</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>44529</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44599</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44529</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44594</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44594</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>44795</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>45365</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45359</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>45533</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>45534</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45426</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44837</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45625</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30123,7 +30123,7 @@
         <v>45267</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45063</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45532</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45670</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45191</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>45183</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>45231</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45351</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45419</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>45419</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45583</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>45743</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45278</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45280</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>45484</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45419</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>45638</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>44951</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>44923</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>45170</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45511</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>44712</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44909</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>44909</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31930,7 +31930,7 @@
         <v>45203</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>44487</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32076,7 +32076,7 @@
         <v>45258</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>44740</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32222,7 +32222,7 @@
         <v>45268</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45387</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>45343</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45426</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>45611</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>45119</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45701</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45568</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32811,7 +32811,7 @@
         <v>45539</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45370</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>44715</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>45289</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45279</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>45131</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45356</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>45009</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>45306</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>45548</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>45708</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>45082</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>45630</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>45154</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>46139</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33926,7 +33926,7 @@
         <v>46031</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45595</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>46136</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>45712</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>46136</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45526</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45786</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>46136</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>46136</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>46139</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>45749</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>45476</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45586</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>46136</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>46136</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45042</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45815</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>46139</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45327</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>46136</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45670</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45525</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>45888</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>45890</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>45890</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>46136</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>46136</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>45294</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         <v>45895</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45895</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44853</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44909</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45895</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>46136</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>45838</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>46136</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>46136</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>45897</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>46136</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45896</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>46139</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>45897</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45897</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45201</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45390</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45217</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>46136</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>45898</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>45898</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>45805</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45294</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45989</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45996</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45812</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45581</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>45730</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38149,7 +38149,7 @@
         <v>45293</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>46090</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38300,7 +38300,7 @@
         <v>45903</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45455</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>45455</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38524,7 +38524,7 @@
         <v>45266</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38597,7 +38597,7 @@
         <v>45905</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45905</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38748,7 +38748,7 @@
         <v>45908</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45911</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>45911</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38967,7 +38967,7 @@
         <v>45911</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>46142</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>46121</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         <v>46142</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39264,7 +39264,7 @@
         <v>46142</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39337,7 +39337,7 @@
         <v>45915</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>45915</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>46146</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>46146</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>46146</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>45693</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39780,7 +39780,7 @@
         <v>46147</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>45483</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44903</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45919</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45919</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45351</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45919</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>45923</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>45922</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>45264</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45266</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45266</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>44902</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>46146</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40827,7 +40827,7 @@
         <v>45215</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>44902</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40973,7 +40973,7 @@
         <v>44606</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41046,7 +41046,7 @@
         <v>46148</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41119,7 +41119,7 @@
         <v>46153</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45930</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45931</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>45930</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45931</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>46153</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>46153</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45933</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41713,7 +41713,7 @@
         <v>44775</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>45407</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>45351</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>45265</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>45553</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>45219</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>45943</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45943</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>45944</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>45911</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42453,7 +42453,7 @@
         <v>45945</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>44685</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45947</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>45903</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45945</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42833,7 +42833,7 @@
         <v>45947</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45947</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>45947</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45950</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45986</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>46153</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45950</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>45953</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45952</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>46070</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45952</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>45953</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45954</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45957</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45202</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>46157</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45958</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>45958</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45208</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45208</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>45674</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>45959</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45958</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45595</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>45524</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45050</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>44979</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44854,7 +44854,7 @@
         <v>46161</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44932,7 +44932,7 @@
         <v>45961</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45005,7 +45005,7 @@
         <v>46161</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45280</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>45280</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>45636</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45966</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45380,7 +45380,7 @@
         <v>46161</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45971</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>46162</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45330</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>46162</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45749</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45974</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45975</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45974</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>45141</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>46163</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>46162</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>44825</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>46163</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45979</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>45979</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>46163</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45981</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>45981</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45980</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45390</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>45027</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47011,7 +47011,7 @@
         <v>45630</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>45533</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
         <v>45742</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>45987</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47308,7 +47308,7 @@
         <v>45147</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47381,7 +47381,7 @@
         <v>45191</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>46164</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>45987</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>45986</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>45989</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>45989</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47829,7 +47829,7 @@
         <v>46164</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45988</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45988</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>45988</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48121,7 +48121,7 @@
         <v>45992</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48194,7 +48194,7 @@
         <v>46169</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48272,7 +48272,7 @@
         <v>45992</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>46168</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>46169</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45995</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>46001</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48637,7 +48637,7 @@
         <v>46168</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48710,7 +48710,7 @@
         <v>45741</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>46001</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>46001</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>46170</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>45058</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>44776</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45202</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>46002</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>46003</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
         <v>46003</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>46003</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>46034</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>46006</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45891</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>46174</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49835,7 +49835,7 @@
         <v>45001</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>45686</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>45700</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>46010</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45729</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45922</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50273,7 +50273,7 @@
         <v>46171</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50351,7 +50351,7 @@
         <v>46014</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50424,7 +50424,7 @@
         <v>46174</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>46174</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50580,7 +50580,7 @@
         <v>46174</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>45866</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45933</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50814,7 +50814,7 @@
         <v>45922</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45933</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45999</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>46171</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45929</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>45968</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>45979</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45895</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>45932</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>45968</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51594,7 +51594,7 @@
         <v>45915</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>44575</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>44575</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>45679</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>44914</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>45399</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52042,7 +52042,7 @@
         <v>45199</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52120,7 +52120,7 @@
         <v>45940</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52198,7 +52198,7 @@
         <v>45985</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52276,7 +52276,7 @@
         <v>46029</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52349,7 +52349,7 @@
         <v>46031</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45534</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52495,7 +52495,7 @@
         <v>45804</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>46031</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>46035</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52719,7 +52719,7 @@
         <v>44586</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>46176</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52870,7 +52870,7 @@
         <v>46035</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52943,7 +52943,7 @@
         <v>45726</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>46175</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53094,7 +53094,7 @@
         <v>46085</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53167,7 +53167,7 @@
         <v>46175</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>46175</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53323,7 +53323,7 @@
         <v>46034</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>46034</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>46036</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>46177</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45860</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45856</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53771,7 +53771,7 @@
         <v>45989</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53844,7 +53844,7 @@
         <v>46105</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53917,7 +53917,7 @@
         <v>45294</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45153</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>46041</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>46043</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45120</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>46043</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45804</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54433,7 +54433,7 @@
         <v>46083</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54506,7 +54506,7 @@
         <v>45355</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54579,7 +54579,7 @@
         <v>46049</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>45499</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54735,7 +54735,7 @@
         <v>46048</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>45825</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>46050</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>46182</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>46051</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>46055</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>45594</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55251,7 +55251,7 @@
         <v>46052</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55324,7 +55324,7 @@
         <v>46052</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>46055</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55475,7 +55475,7 @@
         <v>45040</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55548,7 +55548,7 @@
         <v>46052</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55621,7 +55621,7 @@
         <v>45985</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55694,7 +55694,7 @@
         <v>46057</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55767,7 +55767,7 @@
         <v>46184</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55845,7 +55845,7 @@
         <v>46184</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55923,7 +55923,7 @@
         <v>44924</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>46063</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56074,7 +56074,7 @@
         <v>46065</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>46185</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>46066</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56298,7 +56298,7 @@
         <v>45470</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56371,7 +56371,7 @@
         <v>45474</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56444,7 +56444,7 @@
         <v>46069</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56522,7 +56522,7 @@
         <v>46070</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45236</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56678,7 +56678,7 @@
         <v>45236</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>46070</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>46188</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>44895</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56980,7 +56980,7 @@
         <v>46188</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>45335</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57131,7 +57131,7 @@
         <v>45086</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>46078</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>46188</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>46079</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57423,7 +57423,7 @@
         <v>46079</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57496,7 +57496,7 @@
         <v>46079</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57569,7 +57569,7 @@
         <v>45387</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57642,7 +57642,7 @@
         <v>45219</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57715,7 +57715,7 @@
         <v>46079</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57788,7 +57788,7 @@
         <v>46079</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57861,7 +57861,7 @@
         <v>46080</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57934,7 +57934,7 @@
         <v>46079</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>46080</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>46083</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>46083</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>46083</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -58304,7 +58304,7 @@
         <v>46083</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -58377,7 +58377,7 @@
         <v>46083</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -58450,7 +58450,7 @@
         <v>46083</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45078</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>44994</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>46085</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>46086</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>46085</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>46086</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58966,7 +58966,7 @@
         <v>46090</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -59044,7 +59044,7 @@
         <v>45638</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45008</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -59190,7 +59190,7 @@
         <v>45060</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -59263,7 +59263,7 @@
         <v>46092</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -59341,7 +59341,7 @@
         <v>46091</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -59414,7 +59414,7 @@
         <v>45170</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59487,7 +59487,7 @@
         <v>46093</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>46093</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59643,7 +59643,7 @@
         <v>45664</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>46093</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59794,7 +59794,7 @@
         <v>46093</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59872,7 +59872,7 @@
         <v>45686</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59945,7 +59945,7 @@
         <v>46093</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -60023,7 +60023,7 @@
         <v>46093</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -60101,7 +60101,7 @@
         <v>46191</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -60179,7 +60179,7 @@
         <v>46093</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -60257,7 +60257,7 @@
         <v>45169</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -60335,7 +60335,7 @@
         <v>46098</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -60408,7 +60408,7 @@
         <v>45673</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60486,7 +60486,7 @@
         <v>46196</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>44575</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60632,7 +60632,7 @@
         <v>46196</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60710,7 +60710,7 @@
         <v>46104</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60783,7 +60783,7 @@
         <v>45391</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>46104</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60939,7 +60939,7 @@
         <v>46104</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -61012,7 +61012,7 @@
         <v>46196</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -61090,7 +61090,7 @@
         <v>46196</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -61168,7 +61168,7 @@
         <v>45539</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -61246,7 +61246,7 @@
         <v>46104</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -61319,7 +61319,7 @@
         <v>44740</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -61392,7 +61392,7 @@
         <v>45678</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>46105</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>46105</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
         <v>45631</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61689,7 +61689,7 @@
         <v>46197</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61762,7 +61762,7 @@
         <v>46198</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61840,7 +61840,7 @@
         <v>46198</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61918,7 +61918,7 @@
         <v>45909</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>46198</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -62064,7 +62064,7 @@
         <v>46197</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -62137,7 +62137,7 @@
         <v>46197</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>46197</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -62293,7 +62293,7 @@
         <v>46111</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -62371,7 +62371,7 @@
         <v>46045</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -62449,7 +62449,7 @@
         <v>46114</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>46197</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62595,7 +62595,7 @@
         <v>45561</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>46200</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>46120</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62824,7 +62824,7 @@
         <v>46199</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>44987</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62975,7 +62975,7 @@
         <v>46120</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -63053,7 +63053,7 @@
         <v>46121</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -63131,7 +63131,7 @@
         <v>46125</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -63204,7 +63204,7 @@
         <v>46125</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -63277,7 +63277,7 @@
         <v>45355</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>46127</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -63428,7 +63428,7 @@
         <v>46127</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>46127</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63584,7 +63584,7 @@
         <v>45170</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63657,7 +63657,7 @@
         <v>46128</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63735,7 +63735,7 @@
         <v>45653</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63808,7 +63808,7 @@
         <v>46127</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>46127</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63959,7 +63959,7 @@
         <v>46127</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -64037,7 +64037,7 @@
         <v>46199</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -64115,7 +64115,7 @@
         <v>45992</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -64193,7 +64193,7 @@
         <v>45289</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -64266,7 +64266,7 @@
         <v>46204</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -64344,7 +64344,7 @@
         <v>44929</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -64417,7 +64417,7 @@
         <v>46134</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64495,7 +64495,7 @@
         <v>46204</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64573,7 +64573,7 @@
         <v>46135</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64651,7 +64651,7 @@
         <v>46134</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64729,7 +64729,7 @@
         <v>46136</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64802,7 +64802,7 @@
         <v>46139</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64875,7 +64875,7 @@
         <v>46206</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64953,7 +64953,7 @@
         <v>46139</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -65026,7 +65026,7 @@
         <v>46139</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -65099,7 +65099,7 @@
         <v>46010</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -65172,7 +65172,7 @@
         <v>46205</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -65250,7 +65250,7 @@
         <v>46206</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -65328,7 +65328,7 @@
         <v>45742</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -65406,7 +65406,7 @@
         <v>45233</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65479,7 +65479,7 @@
         <v>46211</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65557,7 +65557,7 @@
         <v>46211</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65635,7 +65635,7 @@
         <v>46212</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65708,7 +65708,7 @@
         <v>46211</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65786,7 +65786,7 @@
         <v>46216</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65864,7 +65864,7 @@
         <v>46213</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65942,7 +65942,7 @@
         <v>44823</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -66015,7 +66015,7 @@
         <v>45441</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -66088,7 +66088,7 @@
         <v>46216</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -66166,7 +66166,7 @@
         <v>45450</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>44874</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -66312,7 +66312,7 @@
         <v>46221</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -66390,7 +66390,7 @@
         <v>44998</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -66463,7 +66463,7 @@
         <v>46225</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66541,7 +66541,7 @@
         <v>45756</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66614,7 +66614,7 @@
         <v>45714</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66692,7 +66692,7 @@
         <v>45279</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66765,7 +66765,7 @@
         <v>46232</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66838,7 +66838,7 @@
         <v>46275</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66911,7 +66911,7 @@
         <v>45548</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66984,7 +66984,7 @@
         <v>45217</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -67057,7 +67057,7 @@
         <v>45320</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -67135,7 +67135,7 @@
         <v>46216</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -67208,7 +67208,7 @@
         <v>46276</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -67281,7 +67281,7 @@
         <v>46105</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -67354,7 +67354,7 @@
         <v>46276</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -67427,7 +67427,7 @@
         <v>45642</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67500,7 +67500,7 @@
         <v>46279</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67573,7 +67573,7 @@
         <v>46279</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67646,7 +67646,7 @@
         <v>44712</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67719,7 +67719,7 @@
         <v>46238</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67797,7 +67797,7 @@
         <v>46238</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67875,7 +67875,7 @@
         <v>46276</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67948,7 +67948,7 @@
         <v>46280</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -68021,7 +68021,7 @@
         <v>45009</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -68094,7 +68094,7 @@
         <v>45280</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -68172,7 +68172,7 @@
         <v>45280</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -68250,7 +68250,7 @@
         <v>46281</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -68323,7 +68323,7 @@
         <v>46280</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -68396,7 +68396,7 @@
         <v>45166</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68474,7 +68474,7 @@
         <v>46281</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68552,7 +68552,7 @@
         <v>46282</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68625,7 +68625,7 @@
         <v>46282</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68698,7 +68698,7 @@
         <v>46239</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68771,7 +68771,7 @@
         <v>44594</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68844,7 +68844,7 @@
         <v>45742</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68922,7 +68922,7 @@
         <v>45171</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68995,7 +68995,7 @@
         <v>44564</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -69068,7 +69068,7 @@
         <v>46287</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -69141,7 +69141,7 @@
         <v>46241</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -69214,7 +69214,7 @@
         <v>44575</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -69287,7 +69287,7 @@
         <v>45231</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -69360,7 +69360,7 @@
         <v>46244</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69438,7 +69438,7 @@
         <v>46244</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69516,7 +69516,7 @@
         <v>45685</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69589,7 +69589,7 @@
         <v>46244</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69667,7 +69667,7 @@
         <v>44974</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69740,7 +69740,7 @@
         <v>45751</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69813,7 +69813,7 @@
         <v>46241</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69886,7 +69886,7 @@
         <v>46289</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69964,7 +69964,7 @@
         <v>44610</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -70037,7 +70037,7 @@
         <v>46246</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -70115,7 +70115,7 @@
         <v>46246</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -70193,7 +70193,7 @@
         <v>46245</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -70271,7 +70271,7 @@
         <v>45327</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -70344,7 +70344,7 @@
         <v>46246</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -70417,7 +70417,7 @@
         <v>46288</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70495,7 +70495,7 @@
         <v>45917</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70568,7 +70568,7 @@
         <v>46248</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70641,7 +70641,7 @@
         <v>45590</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70714,7 +70714,7 @@
         <v>45202</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70787,7 +70787,7 @@
         <v>46248</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70865,7 +70865,7 @@
         <v>46248</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70943,7 +70943,7 @@
         <v>45932</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -71021,7 +71021,7 @@
         <v>46287</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -71094,7 +71094,7 @@
         <v>45293</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -71167,7 +71167,7 @@
         <v>45182</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -71240,7 +71240,7 @@
         <v>46294</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -71313,7 +71313,7 @@
         <v>45516</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -71386,7 +71386,7 @@
         <v>45749</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71459,7 +71459,7 @@
         <v>45674</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71532,7 +71532,7 @@
         <v>45351</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71610,7 +71610,7 @@
         <v>46252</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71683,7 +71683,7 @@
         <v>45289</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71756,7 +71756,7 @@
         <v>46294</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71829,7 +71829,7 @@
         <v>45771</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71907,7 +71907,7 @@
         <v>46297</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71985,7 +71985,7 @@
         <v>46254</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -72058,7 +72058,7 @@
         <v>46253</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -72131,7 +72131,7 @@
         <v>46297</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -72204,7 +72204,7 @@
         <v>46253</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -72282,7 +72282,7 @@
         <v>44907</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -72355,7 +72355,7 @@
         <v>45198</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -72433,7 +72433,7 @@
         <v>45205</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -72506,7 +72506,7 @@
         <v>44810</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -72579,7 +72579,7 @@
         <v>45638</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -72652,7 +72652,7 @@
         <v>45770</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -72730,7 +72730,7 @@
         <v>45915</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -72803,7 +72803,7 @@
         <v>46174</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72876,7 +72876,7 @@
         <v>45359</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -72949,7 +72949,7 @@
         <v>45779</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -73027,7 +73027,7 @@
         <v>45780</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -73100,7 +73100,7 @@
         <v>46300</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -73173,7 +73173,7 @@
         <v>45119</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -73246,7 +73246,7 @@
         <v>46300</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -73319,7 +73319,7 @@
         <v>45785</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -73397,7 +73397,7 @@
         <v>46301</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -73475,7 +73475,7 @@
         <v>46300</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -73548,7 +73548,7 @@
         <v>45582</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -73621,7 +73621,7 @@
         <v>46301</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -73699,7 +73699,7 @@
         <v>46199</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -73777,7 +73777,7 @@
         <v>46288</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -73850,7 +73850,7 @@
         <v>45873</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73923,7 +73923,7 @@
         <v>46294</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -73996,7 +73996,7 @@
         <v>46294</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -74069,7 +74069,7 @@
         <v>46296</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -74147,7 +74147,7 @@
         <v>46255</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -74220,7 +74220,7 @@
         <v>46302</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -74298,7 +74298,7 @@
         <v>46259</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -74371,7 +74371,7 @@
         <v>45789</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -74449,7 +74449,7 @@
         <v>45789</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -74527,7 +74527,7 @@
         <v>46301</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -74600,7 +74600,7 @@
         <v>46260</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -74678,7 +74678,7 @@
         <v>45526</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -74751,7 +74751,7 @@
         <v>46259</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -74824,7 +74824,7 @@
         <v>45790</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74897,7 +74897,7 @@
         <v>45790</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -74975,7 +74975,7 @@
         <v>45790</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -75048,7 +75048,7 @@
         <v>46260</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -75126,7 +75126,7 @@
         <v>45793</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -75204,7 +75204,7 @@
         <v>46262</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -75282,7 +75282,7 @@
         <v>45795</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -75360,7 +75360,7 @@
         <v>46262</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -75433,7 +75433,7 @@
         <v>46262</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -75506,7 +75506,7 @@
         <v>44704</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -75584,7 +75584,7 @@
         <v>45795</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -75662,7 +75662,7 @@
         <v>45794</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -75740,7 +75740,7 @@
         <v>46261</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -75813,7 +75813,7 @@
         <v>46276</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75886,7 +75886,7 @@
         <v>46261</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75959,7 +75959,7 @@
         <v>46261</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -76032,7 +76032,7 @@
         <v>45799</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -76110,7 +76110,7 @@
         <v>45799</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -76188,7 +76188,7 @@
         <v>45799</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -76266,7 +76266,7 @@
         <v>46304</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -76344,7 +76344,7 @@
         <v>45259</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -76417,7 +76417,7 @@
         <v>46265</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -76495,7 +76495,7 @@
         <v>45483</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -76568,7 +76568,7 @@
         <v>45441</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -76641,7 +76641,7 @@
         <v>46308</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -76714,7 +76714,7 @@
         <v>46265</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -76792,7 +76792,7 @@
         <v>46266</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -76870,7 +76870,7 @@
         <v>46265</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76948,7 +76948,7 @@
         <v>45804</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -77026,7 +77026,7 @@
         <v>45804</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -77104,7 +77104,7 @@
         <v>44512</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -77177,7 +77177,7 @@
         <v>45804</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -77255,7 +77255,7 @@
         <v>45805</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -77328,7 +77328,7 @@
         <v>46248</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -77401,7 +77401,7 @@
         <v>45806</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -77479,7 +77479,7 @@
         <v>45806</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -77557,7 +77557,7 @@
         <v>45523</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -77630,7 +77630,7 @@
         <v>45810</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -77708,7 +77708,7 @@
         <v>46265</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -77786,7 +77786,7 @@
         <v>45811</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -77864,7 +77864,7 @@
         <v>46309</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77942,7 +77942,7 @@
         <v>46262</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -78020,7 +78020,7 @@
         <v>46297</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -78093,7 +78093,7 @@
         <v>45813</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -78171,7 +78171,7 @@
         <v>46311</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -78244,7 +78244,7 @@
         <v>45813</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -78322,7 +78322,7 @@
         <v>45812</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -78395,7 +78395,7 @@
         <v>45818</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -78473,7 +78473,7 @@
         <v>45818</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -78551,7 +78551,7 @@
         <v>45819</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -78629,7 +78629,7 @@
         <v>45818</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -78707,7 +78707,7 @@
         <v>45823</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -78785,7 +78785,7 @@
         <v>46310</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -78863,7 +78863,7 @@
         <v>45824</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78936,7 +78936,7 @@
         <v>45824</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -79009,7 +79009,7 @@
         <v>45823</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -79087,7 +79087,7 @@
         <v>45827</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -79165,7 +79165,7 @@
         <v>45826</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -79238,7 +79238,7 @@
         <v>45826</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -79311,7 +79311,7 @@
         <v>45832</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -79389,7 +79389,7 @@
         <v>45832</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -79467,7 +79467,7 @@
         <v>45835</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -79540,7 +79540,7 @@
         <v>45839</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -79613,7 +79613,7 @@
         <v>45819</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -79691,7 +79691,7 @@
         <v>45839</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -79764,7 +79764,7 @@
         <v>45842</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -79837,7 +79837,7 @@
         <v>45842</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -79910,7 +79910,7 @@
         <v>45845</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -79983,7 +79983,7 @@
         <v>45842</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -80056,7 +80056,7 @@
         <v>45845</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -80129,7 +80129,7 @@
         <v>45849</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -80207,7 +80207,7 @@
         <v>45853</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -80280,7 +80280,7 @@
         <v>45854</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -80353,7 +80353,7 @@
         <v>45854</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -80426,7 +80426,7 @@
         <v>45859</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -80499,7 +80499,7 @@
         <v>45875</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -80577,7 +80577,7 @@
         <v>45873</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -80655,7 +80655,7 @@
         <v>45877</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -80733,7 +80733,7 @@
         <v>45481</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -80806,7 +80806,7 @@
         <v>45877</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -80884,7 +80884,7 @@
         <v>45882</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -80962,7 +80962,7 @@
         <v>45883</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -81040,7 +81040,7 @@
         <v>45883</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -81118,7 +81118,7 @@
         <v>45883</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -81196,7 +81196,7 @@
         <v>45882</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -81274,7 +81274,7 @@
         <v>45463</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -81347,7 +81347,7 @@
         <v>45390</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -81420,7 +81420,7 @@
         <v>45323</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -81498,7 +81498,7 @@
         <v>45372</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -81571,7 +81571,7 @@
         <v>45744</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -81644,7 +81644,7 @@
         <v>45748</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -81717,7 +81717,7 @@
         <v>45782</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -81790,7 +81790,7 @@
         <v>46146</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -601,7 +601,7 @@
         <v>45954</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45110</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45419</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45586</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45376</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46164</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>46254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46309</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44853</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>45952</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>45469</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>46274</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>46164</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44966</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45875</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>46170</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45751</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>46310</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>45979</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>45880</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>45875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45422</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>46188</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>45679</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>46301</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44853</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>46240</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>45804</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>46253</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45819</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45519</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>45517</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45943</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>45939</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>44966</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45932</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45875</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45813</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44953</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>45889</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45412</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>46205</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>45783</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45804</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45813</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44966</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>45456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45999</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45782</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>45118</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>46091</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45678</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>45940</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>46301</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>46268</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>46164</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45932</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>45776</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44776</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45187</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>46195</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45945</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>45412</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>46177</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45856</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45944</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>45936</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>45813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>44806</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>45385</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44806</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>46253</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>46128</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45771</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44602</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>45936</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>44806</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44928</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45994</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44900</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>45450</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44712</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44607</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44845</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>46178</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>46244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>46045</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45834</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45834</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45772</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45545</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>46029</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>44572</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>44943</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44503</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45769</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>45944</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>46176</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44529</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45954</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>46237</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>46237</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>46178</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>45985</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>46262</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45811</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45209</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45236</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44860</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45118</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45015</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44791</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>45555</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45904</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>44986</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45931</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45931</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44806</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>46064</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45954</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45960</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44978</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>46199</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>46198</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>46094</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>46204</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45490</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45989</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45475</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>46134</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>45588</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45782</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45643</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>46233</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45789</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>46244</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>46049</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>46289</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>46246</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>46294</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>46069</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>46241</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>46258</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45868</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45933</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45877</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45818</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>46266</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45237</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>46150</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>46153</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45712</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44875</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45608</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45470</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45478</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45736</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44860</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45016</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45016</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>45904</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>46049</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>44826</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45434</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>44606</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>45533</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>46182</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>46197</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>46204</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>46029</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45511</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45260</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>45959</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45615</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>46282</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>46006</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45960</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>46006</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>45517</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>46006</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>46244</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>46244</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>46294</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>46253</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>45909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45840</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45888</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46107</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>45853</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45856</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>46112</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>46134</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45517</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45527</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>46136</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>46139</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>46136</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45560</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>46139</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45555</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>46153</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>46157</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>45511</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45196</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44529</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45092</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45384</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45439</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>45200</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>45594</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45200</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45236</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45595</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45384</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>45118</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>44546</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>44586</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44575</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44536</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>44579</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44834</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>44587</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44529</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>44839</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44729</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44872</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44564</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44536</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>44573</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44587</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>44810</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44698</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44530</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44615</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>44694</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44575</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44714</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>44847</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44648</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>44839</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44529</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>44599</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>44529</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>44594</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44594</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44795</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45583</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45838</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>45191</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45533</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45888</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>45280</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>45890</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>45327</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>45890</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45883</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45896</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45895</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45895</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45266</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45895</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45280</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45280</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45898</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45370</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>44902</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>45897</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>45897</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>45897</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45898</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44586</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45217</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>44712</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>45883</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>45883</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45236</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>45236</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45042</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>45903</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45905</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>45905</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45908</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>46161</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>46162</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>46161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>46161</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>46162</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>46162</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45911</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45911</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45215</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>45911</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45915</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>46163</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45915</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45674</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>45674</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>46164</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>46164</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>46163</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>46163</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45919</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>46168</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45919</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45171</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45922</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45919</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44575</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>44575</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45923</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>46169</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>46169</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>45009</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>46168</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45636</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45930</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>46170</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>45930</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>46171</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>46171</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>45931</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45638</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45931</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45202</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>46174</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45922</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45933</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>45351</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45399</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>46174</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45804</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>46085</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>46175</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45686</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46034</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>46175</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>46175</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>46174</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>46174</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>45943</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>45911</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45943</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45944</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45804</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45989</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>46177</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>46083</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>46105</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>46176</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45450</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>45426</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>45293</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>45289</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>45387</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45945</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45391</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45945</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45947</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>45950</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45947</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>45950</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>45947</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45947</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>45419</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45952</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>45952</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>46182</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45985</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45825</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45953</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>45040</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45954</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>45953</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45231</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45958</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45700</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45958</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45957</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45958</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>45063</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45199</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>45959</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39609,7 +39609,7 @@
         <v>46185</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>46184</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>46184</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>46188</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45961</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>45082</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>45265</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>46188</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>46188</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45966</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>46191</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45202</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45532</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>44853</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>44823</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         <v>45971</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40802,7 +40802,7 @@
         <v>45355</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>46197</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>46197</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41021,7 +41021,7 @@
         <v>46197</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>45974</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>45909</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45974</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41313,7 +41313,7 @@
         <v>46196</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>46196</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>46196</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>46196</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>46197</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>46197</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>46198</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45534</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45975</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>46200</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>46199</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>46198</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>46199</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>46198</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45979</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42463,7 +42463,7 @@
         <v>45980</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>45387</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>45351</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45979</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42765,7 +42765,7 @@
         <v>45693</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45351</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45568</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>45154</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45749</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>45981</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45981</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>46204</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>46204</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         <v>46205</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45986</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>46206</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45987</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45726</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45988</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45987</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>46206</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45751</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45988</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45988</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45208</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>46211</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45992</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>46211</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>45743</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>46211</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45989</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45989</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>46212</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>45231</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>46216</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45685</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>46213</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45995</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>46216</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45741</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>45516</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45742</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45219</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>46002</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>46221</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>44776</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>46001</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>46001</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>46001</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>46225</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45359</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>44998</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>46003</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46505,7 +46505,7 @@
         <v>45780</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>45756</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45279</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>46003</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>46003</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45779</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>46006</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45891</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45119</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46232</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>46279</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>46010</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45785</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>46014</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>46216</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>46280</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>46279</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45866</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45582</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>45933</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>45968</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>45922</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45895</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>46105</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45968</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>45999</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>46238</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45932</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>46281</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>45933</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>45979</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45929</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45915</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>46276</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>46280</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>46238</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49228,7 +49228,7 @@
         <v>46281</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>44895</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49374,7 +49374,7 @@
         <v>45789</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45789</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>46282</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>46282</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45790</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45790</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45790</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45940</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>46239</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>46029</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45985</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>46034</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>46031</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>46031</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>46034</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45526</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45419</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>46035</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50718,7 +50718,7 @@
         <v>46035</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>46036</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45795</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45795</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51020,7 +51020,7 @@
         <v>46241</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45860</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51171,7 +51171,7 @@
         <v>45794</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45856</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>46241</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>46041</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>46245</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45793</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>46043</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>46043</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>46287</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>46244</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>46288</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45441</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45483</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52150,7 +52150,7 @@
         <v>46048</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45799</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>45799</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>46244</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         <v>46244</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45799</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52613,7 +52613,7 @@
         <v>46246</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
         <v>46049</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45259</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52837,7 +52837,7 @@
         <v>46050</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52910,7 +52910,7 @@
         <v>44512</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>45804</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>46052</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53134,7 +53134,7 @@
         <v>46052</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>46246</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53285,7 +53285,7 @@
         <v>45804</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>46052</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53436,7 +53436,7 @@
         <v>46051</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53509,7 +53509,7 @@
         <v>45804</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>46248</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>46055</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53738,7 +53738,7 @@
         <v>45806</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53816,7 +53816,7 @@
         <v>46246</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45806</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53972,7 +53972,7 @@
         <v>46055</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54050,7 +54050,7 @@
         <v>45805</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54123,7 +54123,7 @@
         <v>46057</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54196,7 +54196,7 @@
         <v>45523</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54269,7 +54269,7 @@
         <v>46289</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54347,7 +54347,7 @@
         <v>45810</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>46287</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45812</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>45917</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>45811</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>46063</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>45813</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45813</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54956,7 +54956,7 @@
         <v>46248</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>46066</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45818</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45818</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55263,7 +55263,7 @@
         <v>46294</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>46065</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55409,7 +55409,7 @@
         <v>46248</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>46070</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55565,7 +55565,7 @@
         <v>46070</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>46069</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55721,7 +55721,7 @@
         <v>45818</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45932</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55877,7 +55877,7 @@
         <v>45819</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45824</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>45824</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>45823</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56179,7 +56179,7 @@
         <v>45823</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45484</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45826</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56408,7 +56408,7 @@
         <v>46079</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>46253</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56554,7 +56554,7 @@
         <v>46078</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>46079</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56700,7 +56700,7 @@
         <v>45826</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56773,7 +56773,7 @@
         <v>46294</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>46083</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56919,7 +56919,7 @@
         <v>46083</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56992,7 +56992,7 @@
         <v>46079</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>46079</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57138,7 +57138,7 @@
         <v>46083</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57211,7 +57211,7 @@
         <v>46079</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>46080</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57357,7 +57357,7 @@
         <v>45827</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>46083</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57508,7 +57508,7 @@
         <v>46083</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57581,7 +57581,7 @@
         <v>46083</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>46252</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57732,7 +57732,7 @@
         <v>46253</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57810,7 +57810,7 @@
         <v>46079</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57883,7 +57883,7 @@
         <v>46080</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>45832</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>45832</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -58112,7 +58112,7 @@
         <v>45476</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -58185,7 +58185,7 @@
         <v>46085</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -58258,7 +58258,7 @@
         <v>46085</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -58336,7 +58336,7 @@
         <v>46199</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -58414,7 +58414,7 @@
         <v>46086</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -58487,7 +58487,7 @@
         <v>46300</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>46297</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>46086</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58706,7 +58706,7 @@
         <v>46091</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>46090</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>46174</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58930,7 +58930,7 @@
         <v>45835</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>46093</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -59081,7 +59081,7 @@
         <v>46092</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -59159,7 +59159,7 @@
         <v>46300</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -59232,7 +59232,7 @@
         <v>46093</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -59310,7 +59310,7 @@
         <v>46093</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>46093</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -59466,7 +59466,7 @@
         <v>46093</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -59544,7 +59544,7 @@
         <v>45839</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>46254</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59690,7 +59690,7 @@
         <v>46300</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59763,7 +59763,7 @@
         <v>46093</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59841,7 +59841,7 @@
         <v>46093</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>46297</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>45686</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>45819</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>45839</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>45842</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -60294,7 +60294,7 @@
         <v>46296</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -60372,7 +60372,7 @@
         <v>45842</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>44810</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -60518,7 +60518,7 @@
         <v>46098</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>45842</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>45873</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>45915</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>45845</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60883,7 +60883,7 @@
         <v>45845</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>46255</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -61029,7 +61029,7 @@
         <v>45483</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>45499</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>46104</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>46105</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>46105</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         <v>46104</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>46104</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -61550,7 +61550,7 @@
         <v>46104</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>46301</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61701,7 +61701,7 @@
         <v>45335</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61779,7 +61779,7 @@
         <v>46301</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>45849</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61935,7 +61935,7 @@
         <v>44575</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>44575</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>45548</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>46259</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -62227,7 +62227,7 @@
         <v>46259</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -62300,7 +62300,7 @@
         <v>45854</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -62373,7 +62373,7 @@
         <v>45853</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -62446,7 +62446,7 @@
         <v>46302</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -62524,7 +62524,7 @@
         <v>45854</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>46111</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>46294</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62748,7 +62748,7 @@
         <v>46294</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
         <v>46301</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>46045</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>46288</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>45859</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>46114</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -63191,7 +63191,7 @@
         <v>46261</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -63264,7 +63264,7 @@
         <v>46261</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>44874</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -63410,7 +63410,7 @@
         <v>44704</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>46120</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63561,7 +63561,7 @@
         <v>46120</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63639,7 +63639,7 @@
         <v>44564</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>46121</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>46125</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>46125</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
         <v>46304</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -64014,7 +64014,7 @@
         <v>46260</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>46261</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -64165,7 +64165,7 @@
         <v>46127</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>46127</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -64321,7 +64321,7 @@
         <v>46127</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -64399,7 +64399,7 @@
         <v>45873</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>46260</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         <v>46127</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64633,7 +64633,7 @@
         <v>46127</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64711,7 +64711,7 @@
         <v>45642</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         <v>46128</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64862,7 +64862,7 @@
         <v>45875</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64940,7 +64940,7 @@
         <v>45289</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -65013,7 +65013,7 @@
         <v>46127</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>45355</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45877</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>46276</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -65310,7 +65310,7 @@
         <v>46265</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -65388,7 +65388,7 @@
         <v>45481</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -65461,7 +65461,7 @@
         <v>45294</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65539,7 +65539,7 @@
         <v>45877</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65617,7 +65617,7 @@
         <v>45882</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65695,7 +65695,7 @@
         <v>46262</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65773,7 +65773,7 @@
         <v>46262</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65846,7 +65846,7 @@
         <v>46248</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>45882</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65997,7 +65997,7 @@
         <v>44924</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -66070,7 +66070,7 @@
         <v>44909</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -66143,7 +66143,7 @@
         <v>44909</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -66216,7 +66216,7 @@
         <v>44909</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -66289,7 +66289,7 @@
         <v>46262</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -66362,7 +66362,7 @@
         <v>45992</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -66440,7 +66440,7 @@
         <v>46134</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         <v>44610</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66591,7 +66591,7 @@
         <v>46308</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66664,7 +66664,7 @@
         <v>46134</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66742,7 +66742,7 @@
         <v>46265</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66820,7 +66820,7 @@
         <v>46265</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66898,7 +66898,7 @@
         <v>45539</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66976,7 +66976,7 @@
         <v>46136</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -67054,7 +67054,7 @@
         <v>46136</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -67132,7 +67132,7 @@
         <v>46136</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -67205,7 +67205,7 @@
         <v>46136</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -67283,7 +67283,7 @@
         <v>44929</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -67356,7 +67356,7 @@
         <v>45664</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -67429,7 +67429,7 @@
         <v>46136</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -67507,7 +67507,7 @@
         <v>46136</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67585,7 +67585,7 @@
         <v>46262</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67663,7 +67663,7 @@
         <v>46136</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67741,7 +67741,7 @@
         <v>46136</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67819,7 +67819,7 @@
         <v>46265</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67897,7 +67897,7 @@
         <v>46135</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67975,7 +67975,7 @@
         <v>46136</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -68053,7 +68053,7 @@
         <v>46136</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -68131,7 +68131,7 @@
         <v>46136</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -68204,7 +68204,7 @@
         <v>46266</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -68282,7 +68282,7 @@
         <v>46310</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -68360,7 +68360,7 @@
         <v>46136</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -68438,7 +68438,7 @@
         <v>46136</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -68511,7 +68511,7 @@
         <v>46136</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68589,7 +68589,7 @@
         <v>46136</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68662,7 +68662,7 @@
         <v>45742</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68740,7 +68740,7 @@
         <v>46139</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68813,7 +68813,7 @@
         <v>45119</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68886,7 +68886,7 @@
         <v>45390</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68959,7 +68959,7 @@
         <v>45805</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -69032,7 +69032,7 @@
         <v>45786</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -69105,7 +69105,7 @@
         <v>46314</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -69178,7 +69178,7 @@
         <v>46139</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -69256,7 +69256,7 @@
         <v>45327</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -69329,7 +69329,7 @@
         <v>45815</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -69402,7 +69402,7 @@
         <v>46311</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -69475,7 +69475,7 @@
         <v>44594</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69548,7 +69548,7 @@
         <v>46139</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69621,7 +69621,7 @@
         <v>46139</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69694,7 +69694,7 @@
         <v>46139</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69772,7 +69772,7 @@
         <v>44951</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69845,7 +69845,7 @@
         <v>45009</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69918,7 +69918,7 @@
         <v>46031</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69991,7 +69991,7 @@
         <v>46010</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -70064,7 +70064,7 @@
         <v>45595</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -70137,7 +70137,7 @@
         <v>46139</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -70210,7 +70210,7 @@
         <v>46309</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -70288,7 +70288,7 @@
         <v>46318</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -70361,7 +70361,7 @@
         <v>46315</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -70439,7 +70439,7 @@
         <v>46275</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -70512,7 +70512,7 @@
         <v>45586</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70585,7 +70585,7 @@
         <v>46290</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70658,7 +70658,7 @@
         <v>45996</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70736,7 +70736,7 @@
         <v>45989</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70809,7 +70809,7 @@
         <v>46276</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70882,7 +70882,7 @@
         <v>46142</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70955,7 +70955,7 @@
         <v>46142</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -71028,7 +71028,7 @@
         <v>46276</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -71101,7 +71101,7 @@
         <v>46317</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -71174,7 +71174,7 @@
         <v>45730</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -71247,7 +71247,7 @@
         <v>46121</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -71320,7 +71320,7 @@
         <v>44907</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -71393,7 +71393,7 @@
         <v>46142</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -71466,7 +71466,7 @@
         <v>46090</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71544,7 +71544,7 @@
         <v>45359</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71617,7 +71617,7 @@
         <v>45812</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71690,7 +71690,7 @@
         <v>44740</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71763,7 +71763,7 @@
         <v>45679</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71836,7 +71836,7 @@
         <v>46297</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71909,7 +71909,7 @@
         <v>46146</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71982,7 +71982,7 @@
         <v>46146</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -72055,7 +72055,7 @@
         <v>46146</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -72128,7 +72128,7 @@
         <v>46146</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -72201,7 +72201,7 @@
         <v>46290</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -72274,7 +72274,7 @@
         <v>46317</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -72352,7 +72352,7 @@
         <v>46147</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -72425,7 +72425,7 @@
         <v>45267</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -72503,7 +72503,7 @@
         <v>45426</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -72576,7 +72576,7 @@
         <v>46148</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -72649,7 +72649,7 @@
         <v>44994</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -72722,7 +72722,7 @@
         <v>45986</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -72795,7 +72795,7 @@
         <v>46070</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -72868,7 +72868,7 @@
         <v>46153</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72941,7 +72941,7 @@
         <v>45903</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -73019,7 +73019,7 @@
         <v>46153</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -73092,7 +73092,7 @@
         <v>45202</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -73165,7 +73165,7 @@
         <v>46153</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -73243,7 +73243,7 @@
         <v>46153</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -73316,7 +73316,7 @@
         <v>45008</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -73389,7 +73389,7 @@
         <v>45294</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -73467,7 +73467,7 @@
         <v>45219</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -73540,7 +73540,7 @@
         <v>46157</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -73613,7 +73613,7 @@
         <v>44979</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -73686,7 +73686,7 @@
         <v>44902</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -73759,7 +73759,7 @@
         <v>45581</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -73837,7 +73837,7 @@
         <v>45001</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -73910,7 +73910,7 @@
         <v>45356</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73983,7 +73983,7 @@
         <v>45147</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -74056,7 +74056,7 @@
         <v>45712</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -74134,7 +74134,7 @@
         <v>45455</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -74207,7 +74207,7 @@
         <v>45455</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -74280,7 +74280,7 @@
         <v>45729</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -74353,7 +74353,7 @@
         <v>45170</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -74426,7 +74426,7 @@
         <v>45183</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -74504,7 +74504,7 @@
         <v>45701</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -74577,7 +74577,7 @@
         <v>44923</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -74650,7 +74650,7 @@
         <v>45653</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -74723,7 +74723,7 @@
         <v>45708</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -74796,7 +74796,7 @@
         <v>45625</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -74869,7 +74869,7 @@
         <v>45078</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74942,7 +74942,7 @@
         <v>45771</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -75020,7 +75020,7 @@
         <v>45205</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -75093,7 +75093,7 @@
         <v>45670</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -75171,7 +75171,7 @@
         <v>45208</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -75244,7 +75244,7 @@
         <v>45539</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -75322,7 +75322,7 @@
         <v>45474</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -75395,7 +75395,7 @@
         <v>45203</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -75468,7 +75468,7 @@
         <v>45714</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -75546,7 +75546,7 @@
         <v>44825</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -75619,7 +75619,7 @@
         <v>44685</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -75692,7 +75692,7 @@
         <v>45749</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -75765,7 +75765,7 @@
         <v>45264</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -75838,7 +75838,7 @@
         <v>45060</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75911,7 +75911,7 @@
         <v>45441</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75984,7 +75984,7 @@
         <v>44837</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -76057,7 +76057,7 @@
         <v>45365</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -76130,7 +76130,7 @@
         <v>45595</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -76203,7 +76203,7 @@
         <v>45258</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -76276,7 +76276,7 @@
         <v>45526</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -76349,7 +76349,7 @@
         <v>45131</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -76427,7 +76427,7 @@
         <v>45280</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -76500,7 +76500,7 @@
         <v>45280</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -76578,7 +76578,7 @@
         <v>45407</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -76656,7 +76656,7 @@
         <v>45086</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -76729,7 +76729,7 @@
         <v>44987</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -76802,7 +76802,7 @@
         <v>45320</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -76880,7 +76880,7 @@
         <v>44903</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76953,7 +76953,7 @@
         <v>45419</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -77031,7 +77031,7 @@
         <v>45141</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -77109,7 +77109,7 @@
         <v>45525</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -77182,7 +77182,7 @@
         <v>45289</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -77255,7 +77255,7 @@
         <v>45638</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -77328,7 +77328,7 @@
         <v>45120</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -77401,7 +77401,7 @@
         <v>45182</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -77474,7 +77474,7 @@
         <v>45533</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -77547,7 +77547,7 @@
         <v>45191</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -77625,7 +77625,7 @@
         <v>45058</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -77703,7 +77703,7 @@
         <v>45638</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -77776,7 +77776,7 @@
         <v>45590</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -77849,7 +77849,7 @@
         <v>45670</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77922,7 +77922,7 @@
         <v>45630</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77995,7 +77995,7 @@
         <v>45594</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -78068,7 +78068,7 @@
         <v>45678</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -78141,7 +78141,7 @@
         <v>44606</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -78214,7 +78214,7 @@
         <v>45611</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -78292,7 +78292,7 @@
         <v>45673</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -78370,7 +78370,7 @@
         <v>45153</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -78443,7 +78443,7 @@
         <v>45198</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -78521,7 +78521,7 @@
         <v>44775</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -78599,7 +78599,7 @@
         <v>44712</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -78672,7 +78672,7 @@
         <v>45217</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -78745,7 +78745,7 @@
         <v>45233</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -78818,7 +78818,7 @@
         <v>45201</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78896,7 +78896,7 @@
         <v>45170</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -78969,7 +78969,7 @@
         <v>45170</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -79042,7 +79042,7 @@
         <v>45169</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -79120,7 +79120,7 @@
         <v>44740</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -79193,7 +79193,7 @@
         <v>45278</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -79266,7 +79266,7 @@
         <v>45166</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -79344,7 +79344,7 @@
         <v>45770</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -79422,7 +79422,7 @@
         <v>45306</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -79495,7 +79495,7 @@
         <v>45534</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -79568,7 +79568,7 @@
         <v>45294</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -79646,7 +79646,7 @@
         <v>45343</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -79719,7 +79719,7 @@
         <v>45330</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -79792,7 +79792,7 @@
         <v>45630</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -79865,7 +79865,7 @@
         <v>45050</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -79938,7 +79938,7 @@
         <v>45027</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -80011,7 +80011,7 @@
         <v>45351</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -80089,7 +80089,7 @@
         <v>45279</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -80162,7 +80162,7 @@
         <v>45268</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -80235,7 +80235,7 @@
         <v>45293</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -80308,7 +80308,7 @@
         <v>45749</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -80381,7 +80381,7 @@
         <v>44974</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -80454,7 +80454,7 @@
         <v>45631</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -80532,7 +80532,7 @@
         <v>45553</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -80605,7 +80605,7 @@
         <v>45470</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -80678,7 +80678,7 @@
         <v>44914</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -80751,7 +80751,7 @@
         <v>45390</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -80824,7 +80824,7 @@
         <v>45266</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -80897,7 +80897,7 @@
         <v>45266</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -80975,7 +80975,7 @@
         <v>45511</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -81048,7 +81048,7 @@
         <v>45548</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -81121,7 +81121,7 @@
         <v>45561</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -81199,7 +81199,7 @@
         <v>45742</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -81277,7 +81277,7 @@
         <v>45524</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -81350,7 +81350,7 @@
         <v>44715</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -81423,7 +81423,7 @@
         <v>45463</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -81496,7 +81496,7 @@
         <v>45390</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -81569,7 +81569,7 @@
         <v>45323</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -81647,7 +81647,7 @@
         <v>45372</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -81720,7 +81720,7 @@
         <v>45744</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -81793,7 +81793,7 @@
         <v>45748</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -81866,7 +81866,7 @@
         <v>45782</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -81939,7 +81939,7 @@
         <v>46146</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>

--- a/Översikt BERG.xlsx
+++ b/Översikt BERG.xlsx
@@ -601,7 +601,7 @@
         <v>45954</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>45110</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45419</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>45586</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45376</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>46164</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45545</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>46254</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>45517</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>46267</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>46253</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46309</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44853</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>45952</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>45469</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>46274</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>46164</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>45425</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44966</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45875</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>46170</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45751</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>46310</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>45979</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>45880</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>45875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>45323</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>45422</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45889</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>46188</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>45679</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>46301</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>44853</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>46240</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>45804</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>46253</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45819</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>45519</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>45517</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45943</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>45939</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>44966</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45932</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45875</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>45813</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44953</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>45889</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45412</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>46205</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>45783</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>45804</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45813</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44966</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>45456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45999</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45782</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>45118</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>46091</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45678</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>45940</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>46301</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>46268</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>46164</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>45932</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>45776</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44776</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45187</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>46195</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45945</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>45412</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>46177</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45517</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45856</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45944</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>45936</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>45813</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>44806</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>45385</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44806</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>46253</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>46128</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45771</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44602</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>45936</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>44806</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44928</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45994</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44900</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>45450</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44712</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44607</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44845</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>46178</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>46244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>46045</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45834</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45834</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45772</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>45545</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>46029</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>44572</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>44943</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44503</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45769</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>45944</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>46176</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44529</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45954</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>46237</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>46237</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>46178</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>45985</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>46127</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>46262</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45811</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45209</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45236</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44860</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45118</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45015</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44791</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>45555</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>45904</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>44986</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45931</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>45931</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44806</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>46064</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45954</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45960</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44978</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>46199</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>46198</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>46094</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>46204</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45490</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45989</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45475</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>46134</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>45588</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45782</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45643</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>46233</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>45789</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>46244</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>46049</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>46289</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>46246</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>46294</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>46069</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>46241</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>46258</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45868</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45933</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45877</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45818</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>46266</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>45237</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>46150</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>46153</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45712</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44875</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45608</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45470</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45478</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45736</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44860</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45016</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45016</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>45904</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>46049</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>44826</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45434</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         <v>44606</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>45533</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>46182</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>46197</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>46204</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>46029</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45511</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45260</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>45959</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45615</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>46282</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>46006</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45960</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>46006</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>45517</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>46006</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>46244</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>46244</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>46294</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>46253</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>45909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45840</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45888</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46107</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>45853</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>45856</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>46112</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>46134</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45517</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45527</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>46136</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>46139</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>46136</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45560</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>46139</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45555</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>46153</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>46157</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>45511</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45196</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44529</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45092</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45384</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45439</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>45200</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>45594</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45200</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45236</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45595</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45384</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>45118</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>44546</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>44586</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44575</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44536</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>44579</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>44834</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>44587</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44529</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>44839</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44729</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44872</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44564</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>44536</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>44573</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44587</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>44810</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44698</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44530</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>44615</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>44694</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44575</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>44714</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>44847</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>44648</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>44839</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44529</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>44599</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>44529</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>44594</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>44594</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44795</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45583</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45838</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>45191</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45533</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45888</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>45280</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>45890</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>45327</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>45890</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45883</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45896</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>45895</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45895</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45266</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45895</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45280</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45280</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45898</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45370</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>44902</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>45897</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>45897</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>45897</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45898</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44586</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45217</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         <v>44712</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>45883</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>45883</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45236</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>45236</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45042</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>45903</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>45905</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>45905</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45908</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>46161</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>46162</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>46161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>46161</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>46162</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>46162</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32572,7 +32572,7 @@
         <v>45911</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45911</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>45215</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32796,7 +32796,7 @@
         <v>45911</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>45915</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>46163</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>45915</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45674</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>45674</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>46164</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>46164</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>46163</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>46163</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45919</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>46168</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>45919</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45171</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45922</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45919</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44575</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>44575</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>45923</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>46169</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>46169</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>45009</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>46168</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45636</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45930</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>46170</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34729,7 +34729,7 @@
         <v>45930</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34807,7 +34807,7 @@
         <v>46171</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>46171</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34963,7 +34963,7 @@
         <v>45931</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45638</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>45931</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45202</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>46174</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35333,7 +35333,7 @@
         <v>45922</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45933</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>45351</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45399</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>46174</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45804</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>46085</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>46175</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45686</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46034</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>46175</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>46175</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>46174</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>46174</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>45943</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>45911</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45943</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>45944</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45804</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45989</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>46177</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>46083</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>46105</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>46176</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45450</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>45426</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>45293</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>45289</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>45387</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45945</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45391</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45945</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45947</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>45950</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>45947</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>45950</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>45947</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>45947</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>45419</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45952</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>45952</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>46182</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45985</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45825</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>45953</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>45040</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45954</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>45953</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>45231</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45958</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45700</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45958</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45957</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45958</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>45063</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45199</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>45959</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39609,7 +39609,7 @@
         <v>46185</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>46184</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>46184</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>46188</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>45961</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>45082</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>45265</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>46188</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>46188</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45966</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>46191</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45202</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40505,7 +40505,7 @@
         <v>45532</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>44853</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>44823</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         <v>45971</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40802,7 +40802,7 @@
         <v>45355</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40875,7 +40875,7 @@
         <v>46197</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>46197</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41021,7 +41021,7 @@
         <v>46197</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>45974</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>45909</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45974</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41313,7 +41313,7 @@
         <v>46196</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>46196</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>46196</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41542,7 +41542,7 @@
         <v>46196</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>46197</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>46197</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>46198</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>45534</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41932,7 +41932,7 @@
         <v>45975</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>46200</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>46199</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>46198</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>46199</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>46198</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45979</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42463,7 +42463,7 @@
         <v>45980</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>45387</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>45351</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45979</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42765,7 +42765,7 @@
         <v>45693</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45351</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45568</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>45154</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45749</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>45981</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45981</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>46204</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>46204</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43442,7 +43442,7 @@
         <v>46205</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45986</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>46206</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45987</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45726</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45988</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>45987</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>46206</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45751</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45988</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45988</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45208</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>46211</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45992</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>46211</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>45743</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>46211</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45989</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45989</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>46212</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>45231</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>46216</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45685</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>46213</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45995</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>46216</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>45741</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>45516</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45742</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45219</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>46002</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>46221</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>44776</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>46001</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>46001</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>46001</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>46225</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45359</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>44998</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>46003</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46505,7 +46505,7 @@
         <v>45780</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>45756</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45279</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>46003</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>46003</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45779</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>46006</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45891</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45119</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46232</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>46279</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>46010</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45785</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>46014</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>46216</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>46280</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>46279</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45866</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45582</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>45933</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>45968</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>45922</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45895</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>46105</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45968</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>45999</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>46238</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45932</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>46281</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>45933</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>45979</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45929</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45915</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>46276</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>46280</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>46238</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49228,7 +49228,7 @@
         <v>46281</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>44895</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49374,7 +49374,7 @@
         <v>45789</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45789</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>46282</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>46282</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45790</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45790</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49827,7 +49827,7 @@
         <v>45790</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45940</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>46239</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>46029</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45985</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>46034</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>46031</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>46031</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>46034</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45526</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45419</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>46035</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50718,7 +50718,7 @@
         <v>46035</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>46036</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45795</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45795</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51020,7 +51020,7 @@
         <v>46241</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>45860</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51171,7 +51171,7 @@
         <v>45794</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45856</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51327,7 +51327,7 @@
         <v>46241</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51400,7 +51400,7 @@
         <v>46041</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>46245</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45793</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>46043</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>46043</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>46287</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>46244</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51926,7 +51926,7 @@
         <v>46288</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>45441</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>45483</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52150,7 +52150,7 @@
         <v>46048</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45799</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>45799</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>46244</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         <v>46244</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45799</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52613,7 +52613,7 @@
         <v>46246</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
         <v>46049</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45259</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52837,7 +52837,7 @@
         <v>46050</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52910,7 +52910,7 @@
         <v>44512</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>45804</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>46052</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53134,7 +53134,7 @@
         <v>46052</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>46246</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53285,7 +53285,7 @@
         <v>45804</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>46052</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53436,7 +53436,7 @@
         <v>46051</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53509,7 +53509,7 @@
         <v>45804</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>46248</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>46055</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53738,7 +53738,7 @@
         <v>45806</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53816,7 +53816,7 @@
         <v>46246</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53894,7 +53894,7 @@
         <v>45806</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53972,7 +53972,7 @@
         <v>46055</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54050,7 +54050,7 @@
         <v>45805</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54123,7 +54123,7 @@
         <v>46057</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54196,7 +54196,7 @@
         <v>45523</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54269,7 +54269,7 @@
         <v>46289</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54347,7 +54347,7 @@
         <v>45810</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54425,7 +54425,7 @@
         <v>46287</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45812</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54571,7 +54571,7 @@
         <v>45917</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>45811</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54722,7 +54722,7 @@
         <v>46063</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>45813</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54878,7 +54878,7 @@
         <v>45813</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54956,7 +54956,7 @@
         <v>46248</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>46066</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45818</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45818</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55263,7 +55263,7 @@
         <v>46294</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55336,7 +55336,7 @@
         <v>46065</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55409,7 +55409,7 @@
         <v>46248</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55487,7 +55487,7 @@
         <v>46070</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55565,7 +55565,7 @@
         <v>46070</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>46069</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55721,7 +55721,7 @@
         <v>45818</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45932</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55877,7 +55877,7 @@
         <v>45819</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45824</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>45824</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>45823</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56179,7 +56179,7 @@
         <v>45823</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45484</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56335,7 +56335,7 @@
         <v>45826</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56408,7 +56408,7 @@
         <v>46079</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>46253</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56554,7 +56554,7 @@
         <v>46078</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>46079</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56700,7 +56700,7 @@
         <v>45826</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56773,7 +56773,7 @@
         <v>46294</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56846,7 +56846,7 @@
         <v>46083</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56919,7 +56919,7 @@
         <v>46083</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56992,7 +56992,7 @@
         <v>46079</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>46079</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57138,7 +57138,7 @@
         <v>46083</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57211,7 +57211,7 @@
         <v>46079</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57284,7 +57284,7 @@
         <v>46080</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57357,7 +57357,7 @@
         <v>45827</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>46083</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57508,7 +57508,7 @@
         <v>46083</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57581,7 +57581,7 @@
         <v>46083</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57659,7 +57659,7 @@
         <v>46252</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57732,7 +57732,7 @@
         <v>46253</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57810,7 +57810,7 @@
         <v>46079</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57883,7 +57883,7 @@
         <v>46080</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>45832</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>45832</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -58112,7 +58112,7 @@
         <v>45476</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -58185,7 +58185,7 @@
         <v>46085</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -58258,7 +58258,7 @@
         <v>46085</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -58336,7 +58336,7 @@
         <v>46199</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -58414,7 +58414,7 @@
         <v>46086</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -58487,7 +58487,7 @@
         <v>46300</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>46297</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>46086</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58706,7 +58706,7 @@
         <v>46091</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>46090</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>46174</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58930,7 +58930,7 @@
         <v>45835</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>46093</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -59081,7 +59081,7 @@
         <v>46092</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -59159,7 +59159,7 @@
         <v>46300</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -59232,7 +59232,7 @@
         <v>46093</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -59310,7 +59310,7 @@
         <v>46093</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>46093</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -59466,7 +59466,7 @@
         <v>46093</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -59544,7 +59544,7 @@
         <v>45839</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>46254</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59690,7 +59690,7 @@
         <v>46300</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59763,7 +59763,7 @@
         <v>46093</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59841,7 +59841,7 @@
         <v>46093</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>46297</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>45686</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>45819</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>45839</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>45842</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -60294,7 +60294,7 @@
         <v>46296</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -60372,7 +60372,7 @@
         <v>45842</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -60445,7 +60445,7 @@
         <v>44810</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -60518,7 +60518,7 @@
         <v>46098</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>45842</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>45873</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>45915</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>45845</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60883,7 +60883,7 @@
         <v>45845</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>46255</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -61029,7 +61029,7 @@
         <v>45483</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -61102,7 +61102,7 @@
         <v>45499</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>46104</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>46105</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>46105</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         <v>46104</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>46104</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -61550,7 +61550,7 @@
         <v>46104</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>46301</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61701,7 +61701,7 @@
         <v>45335</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61779,7 +61779,7 @@
         <v>46301</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>45849</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61935,7 +61935,7 @@
         <v>44575</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>44575</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>45548</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>46259</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -62227,7 +62227,7 @@
         <v>46259</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -62300,7 +62300,7 @@
         <v>45854</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -62373,7 +62373,7 @@
         <v>45853</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -62446,7 +62446,7 @@
         <v>46302</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -62524,7 +62524,7 @@
         <v>45854</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62597,7 +62597,7 @@
         <v>46111</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>46294</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62748,7 +62748,7 @@
         <v>46294</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
         <v>46301</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>46045</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>46288</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>45859</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>46114</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -63191,7 +63191,7 @@
         <v>46261</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -63264,7 +63264,7 @@
         <v>46261</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>44874</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -63410,7 +63410,7 @@
         <v>44704</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>46120</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63561,7 +63561,7 @@
         <v>46120</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63639,7 +63639,7 @@
         <v>44564</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>46121</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>46125</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>46125</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
         <v>46304</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -64014,7 +64014,7 @@
         <v>46260</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>46261</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -64165,7 +64165,7 @@
         <v>46127</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -64243,7 +64243,7 @@
         <v>46127</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -64321,7 +64321,7 @@
         <v>46127</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -64399,7 +64399,7 @@
         <v>45873</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>46260</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         <v>46127</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64633,7 +64633,7 @@
         <v>46127</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64711,7 +64711,7 @@
         <v>45642</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         <v>46128</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64862,7 +64862,7 @@
         <v>45875</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64940,7 +64940,7 @@
         <v>45289</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -65013,7 +65013,7 @@
         <v>46127</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>45355</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45877</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>46276</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -65310,7 +65310,7 @@
         <v>46265</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -65388,7 +65388,7 @@
         <v>45481</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -65461,7 +65461,7 @@
         <v>45294</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65539,7 +65539,7 @@
         <v>45877</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65617,7 +65617,7 @@
         <v>45882</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65695,7 +65695,7 @@
         <v>46262</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65773,7 +65773,7 @@
         <v>46262</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65846,7 +65846,7 @@
         <v>46248</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>45882</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65997,7 +65997,7 @@
         <v>44924</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -66070,7 +66070,7 @@
         <v>44909</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -66143,7 +66143,7 @@
         <v>44909</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -66216,7 +66216,7 @@
         <v>44909</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -66289,7 +66289,7 @@
         <v>46262</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -66362,7 +66362,7 @@
         <v>45992</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -66440,7 +66440,7 @@
         <v>46134</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         <v>44610</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66591,7 +66591,7 @@
         <v>46308</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66664,7 +66664,7 @@
         <v>46134</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66742,7 +66742,7 @@
         <v>46265</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66820,7 +66820,7 @@
         <v>46265</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66898,7 +66898,7 @@
         <v>45539</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66976,7 +66976,7 @@
         <v>46136</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -67054,7 +67054,7 @@
         <v>46136</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -67132,7 +67132,7 @@
         <v>46136</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -67205,7 +67205,7 @@
         <v>46136</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -67283,7 +67283,7 @@
         <v>44929</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -67356,7 +67356,7 @@
         <v>45664</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -67429,7 +67429,7 @@
         <v>46136</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -67507,7 +67507,7 @@
         <v>46136</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67585,7 +67585,7 @@
         <v>46262</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67663,7 +67663,7 @@
         <v>46136</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67741,7 +67741,7 @@
         <v>46136</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67819,7 +67819,7 @@
         <v>46265</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67897,7 +67897,7 @@
         <v>46135</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67975,7 +67975,7 @@
         <v>46136</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -68053,7 +68053,7 @@
         <v>46136</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -68131,7 +68131,7 @@
         <v>46136</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -68204,7 +68204,7 @@
         <v>46266</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -68282,7 +68282,7 @@
         <v>46310</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -68360,7 +68360,7 @@
         <v>46136</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -68438,7 +68438,7 @@
         <v>46136</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -68511,7 +68511,7 @@
         <v>46136</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68589,7 +68589,7 @@
         <v>46136</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68662,7 +68662,7 @@
         <v>45742</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68740,7 +68740,7 @@
         <v>46139</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68813,7 +68813,7 @@
         <v>45119</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68886,7 +68886,7 @@
         <v>45390</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68959,7 +68959,7 @@
         <v>45805</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -69032,7 +69032,7 @@
         <v>45786</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -69105,7 +69105,7 @@
         <v>46314</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -69178,7 +69178,7 @@
         <v>46139</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -69256,7 +69256,7 @@
         <v>45327</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -69329,7 +69329,7 @@
         <v>45815</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -69402,7 +69402,7 @@
         <v>46311</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -69475,7 +69475,7 @@
         <v>44594</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69548,7 +69548,7 @@
         <v>46139</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69621,7 +69621,7 @@
         <v>46139</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69694,7 +69694,7 @@
         <v>46139</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69772,7 +69772,7 @@
         <v>44951</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69845,7 +69845,7 @@
         <v>45009</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69918,7 +69918,7 @@
         <v>46031</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69991,7 +69991,7 @@
         <v>46010</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -70064,7 +70064,7 @@
         <v>45595</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -70137,7 +70137,7 @@
         <v>46139</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -70210,7 +70210,7 @@
         <v>46309</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -70288,7 +70288,7 @@
         <v>46318</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -70361,7 +70361,7 @@
         <v>46315</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -70439,7 +70439,7 @@
         <v>46275</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -70512,7 +70512,7 @@
         <v>45586</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70585,7 +70585,7 @@
         <v>46290</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70658,7 +70658,7 @@
         <v>45996</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70736,7 +70736,7 @@
         <v>45989</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70809,7 +70809,7 @@
         <v>46276</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70882,7 +70882,7 @@
         <v>46142</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70955,7 +70955,7 @@
         <v>46142</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -71028,7 +71028,7 @@
         <v>46276</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -71101,7 +71101,7 @@
         <v>46317</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -71174,7 +71174,7 @@
         <v>45730</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -71247,7 +71247,7 @@
         <v>46121</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -71320,7 +71320,7 @@
         <v>44907</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -71393,7 +71393,7 @@
         <v>46142</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -71466,7 +71466,7 @@
         <v>46090</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71544,7 +71544,7 @@
         <v>45359</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71617,7 +71617,7 @@
         <v>45812</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71690,7 +71690,7 @@
         <v>44740</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71763,7 +71763,7 @@
         <v>45679</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71836,7 +71836,7 @@
         <v>46297</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71909,7 +71909,7 @@
         <v>46146</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71982,7 +71982,7 @@
         <v>46146</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -72055,7 +72055,7 @@
         <v>46146</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -72128,7 +72128,7 @@
         <v>46146</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -72201,7 +72201,7 @@
         <v>46290</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -72274,7 +72274,7 @@
         <v>46317</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -72352,7 +72352,7 @@
         <v>46147</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -72425,7 +72425,7 @@
         <v>45267</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -72503,7 +72503,7 @@
         <v>45426</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -72576,7 +72576,7 @@
         <v>46148</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -72649,7 +72649,7 @@
         <v>44994</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -72722,7 +72722,7 @@
         <v>45986</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -72795,7 +72795,7 @@
         <v>46070</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -72868,7 +72868,7 @@
         <v>46153</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72941,7 +72941,7 @@
         <v>45903</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -73019,7 +73019,7 @@
         <v>46153</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -73092,7 +73092,7 @@
         <v>45202</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -73165,7 +73165,7 @@
         <v>46153</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -73243,7 +73243,7 @@
         <v>46153</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -73316,7 +73316,7 @@
         <v>45008</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -73389,7 +73389,7 @@
         <v>45294</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -73467,7 +73467,7 @@
         <v>45219</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -73540,7 +73540,7 @@
         <v>46157</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -73613,7 +73613,7 @@
         <v>44979</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -73686,7 +73686,7 @@
         <v>44902</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -73759,7 +73759,7 @@
         <v>45581</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -73837,7 +73837,7 @@
         <v>45001</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -73910,7 +73910,7 @@
         <v>45356</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73983,7 +73983,7 @@
         <v>45147</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -74056,7 +74056,7 @@
         <v>45712</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -74134,7 +74134,7 @@
         <v>45455</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -74207,7 +74207,7 @@
         <v>45455</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -74280,7 +74280,7 @@
         <v>45729</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -74353,7 +74353,7 @@
         <v>45170</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -74426,7 +74426,7 @@
         <v>45183</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -74504,7 +74504,7 @@
         <v>45701</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -74577,7 +74577,7 @@
         <v>44923</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -74650,7 +74650,7 @@
         <v>45653</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -74723,7 +74723,7 @@
         <v>45708</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -74796,7 +74796,7 @@
         <v>45625</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -74869,7 +74869,7 @@
         <v>45078</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74942,7 +74942,7 @@
         <v>45771</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -75020,7 +75020,7 @@
         <v>45205</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -75093,7 +75093,7 @@
         <v>45670</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -75171,7 +75171,7 @@
         <v>45208</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -75244,7 +75244,7 @@
         <v>45539</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -75322,7 +75322,7 @@
         <v>45474</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -75395,7 +75395,7 @@
         <v>45203</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -75468,7 +75468,7 @@
         <v>45714</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -75546,7 +75546,7 @@
         <v>44825</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -75619,7 +75619,7 @@
         <v>44685</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -75692,7 +75692,7 @@
         <v>45749</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -75765,7 +75765,7 @@
         <v>45264</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -75838,7 +75838,7 @@
         <v>45060</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75911,7 +75911,7 @@
         <v>45441</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75984,7 +75984,7 @@
         <v>44837</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -76057,7 +76057,7 @@
         <v>45365</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -76130,7 +76130,7 @@
         <v>45595</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -76203,7 +76203,7 @@
         <v>45258</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -76276,7 +76276,7 @@
         <v>45526</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -76349,7 +76349,7 @@
         <v>45131</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -76427,7 +76427,7 @@
         <v>45280</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -76500,7 +76500,7 @@
         <v>45280</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -76578,7 +76578,7 @@
         <v>45407</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -76656,7 +76656,7 @@
         <v>45086</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -76729,7 +76729,7 @@
         <v>44987</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -76802,7 +76802,7 @@
         <v>45320</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -76880,7 +76880,7 @@
         <v>44903</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76953,7 +76953,7 @@
         <v>45419</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -77031,7 +77031,7 @@
         <v>45141</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -77109,7 +77109,7 @@
         <v>45525</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -77182,7 +77182,7 @@
         <v>45289</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -77255,7 +77255,7 @@
         <v>45638</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -77328,7 +77328,7 @@
         <v>45120</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -77401,7 +77401,7 @@
         <v>45182</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -77474,7 +77474,7 @@
         <v>45533</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -77547,7 +77547,7 @@
         <v>45191</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -77625,7 +77625,7 @@
         <v>45058</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -77703,7 +77703,7 @@
         <v>45638</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -77776,7 +77776,7 @@
         <v>45590</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -77849,7 +77849,7 @@
         <v>45670</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77922,7 +77922,7 @@
         <v>45630</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77995,7 +77995,7 @@
         <v>45594</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -78068,7 +78068,7 @@
         <v>45678</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -78141,7 +78141,7 @@
         <v>44606</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -78214,7 +78214,7 @@
         <v>45611</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -78292,7 +78292,7 @@
         <v>45673</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -78370,7 +78370,7 @@
         <v>45153</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -78443,7 +78443,7 @@
         <v>45198</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -78521,7 +78521,7 @@
         <v>44775</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -78599,7 +78599,7 @@
         <v>44712</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -78672,7 +78672,7 @@
         <v>45217</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -78745,7 +78745,7 @@
         <v>45233</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -78818,7 +78818,7 @@
         <v>45201</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78896,7 +78896,7 @@
         <v>45170</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -78969,7 +78969,7 @@
         <v>45170</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -79042,7 +79042,7 @@
         <v>45169</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -79120,7 +79120,7 @@
         <v>44740</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -79193,7 +79193,7 @@
         <v>45278</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -79266,7 +79266,7 @@
         <v>45166</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -79344,7 +79344,7 @@
         <v>45770</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -79422,7 +79422,7 @@
         <v>45306</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -79495,7 +79495,7 @@
         <v>45534</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -79568,7 +79568,7 @@
         <v>45294</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -79646,7 +79646,7 @@
         <v>45343</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -79719,7 +79719,7 @@
         <v>45330</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -79792,7 +79792,7 @@
         <v>45630</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -79865,7 +79865,7 @@
         <v>45050</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -79938,7 +79938,7 @@
         <v>45027</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -80011,7 +80011,7 @@
         <v>45351</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -80089,7 +80089,7 @@
         <v>45279</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -80162,7 +80162,7 @@
         <v>45268</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -80235,7 +80235,7 @@
         <v>45293</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -80308,7 +80308,7 @@
         <v>45749</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -80381,7 +80381,7 @@
         <v>44974</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -80454,7 +80454,7 @@
         <v>45631</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -80532,7 +80532,7 @@
         <v>45553</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -80605,7 +80605,7 @@
         <v>45470</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -80678,7 +80678,7 @@
         <v>44914</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -80751,7 +80751,7 @@
         <v>45390</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -80824,7 +80824,7 @@
         <v>45266</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -80897,7 +80897,7 @@
         <v>45266</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -80975,7 +80975,7 @@
         <v>45511</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -81048,7 +81048,7 @@
         <v>45548</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -81121,7 +81121,7 @@
         <v>45561</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -81199,7 +81199,7 @@
         <v>45742</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -81277,7 +81277,7 @@
         <v>45524</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -81350,7 +81350,7 @@
         <v>44715</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -81423,7 +81423,7 @@
         <v>45463</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -81496,7 +81496,7 @@
         <v>45390</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -81569,7 +81569,7 @@
         <v>45323</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -81647,7 +81647,7 @@
         <v>45372</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -81720,7 +81720,7 @@
         <v>45744</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -81793,7 +81793,7 @@
         <v>45748</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -81866,7 +81866,7 @@
         <v>45782</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -81939,7 +81939,7 @@
         <v>46146</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
